--- a/PoE2_仕様書.xlsx
+++ b/PoE2_仕様書.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="1088">
   <si>
     <t>No</t>
   </si>
@@ -133,13 +133,13 @@
     <t>クラス</t>
   </si>
   <si>
-    <t>Warrior/Monk/Ranger/Witch/Sorceress/Mercenaryの6クラスを用意し、各クラスは開始位置・武器適性・スキル傾向が異なる。</t>
+    <t xml:space="preserve">Warrior/Monk/Ranger/Witch/Sorceress/Mercenary/Huntressの7クラスを用意し、各クラスは開始位置・武器適性・スキル傾向が異なる。2026年12月のバージョン1.0で8クラス目Duelist(新武器種Sword対応)が追加予定。</t>
   </si>
   <si>
     <t>Ascendancy</t>
   </si>
   <si>
-    <t>各クラスに2種のAscendancyを用意し、ルーグライク試練(Trial of the Sekhemas等)のクリア報酬として最大8ポイントを獲得し専用パッシブを解放する。</t>
+    <t xml:space="preserve">各クラスに2〜3種のAscendancy(クラス・バージョンにより数が異なる)を用意し、ルーグライク試練(Trial of the Sekhemas等)のクリア報酬として最大8ポイントを獲得し専用パッシブを解放する。</t>
   </si>
   <si>
     <t>レベル</t>
@@ -277,10 +277,10 @@
     <t>Ascendancy一覧(参考)</t>
   </si>
   <si>
-    <t>Warrior→Titan/Warbringer、Monk→Invoker/Acolyte of Chayula、Ranger→Deadeye/Pathfinder、Witch→Infernalist/Blood Mage、Sorceress→Stormweaver/Chronomancer、Mercenary→Witchhunter/Gemling Legionnaireの計12種(Early Access時点)。</t>
-  </si>
-  <si>
-    <t>Ascendancy項目(No8)の具体名称を参考情報として付記。今後のアップデートで追加・変更の可能性あり。</t>
+    <t xml:space="preserve">Warrior→Titan/Warbringer/Smith of Kitava、Monk→Invoker/Acolyte of Chayula/Martial Artist、Ranger→Deadeye/Pathfinder、Witch→Infernalist/Blood Mage/Lich、Sorceress→Stormweaver/Chronomancer、Mercenary→Witchhunter/Gemling Legionnaire/Tactician、Huntress→Ritualist/Amazon/Spirit Walkerの計19種、7クラス(2026-09時点、Early Access中)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy項目(No8)の具体名称を参考情報として付記。2026-09時点の内容へ更新(Dawn of the Hunt/Return of the Ancientsの追加分を反映)。1.0(2026-12-11予定)でさらに追加・変更の可能性あり。</t>
   </si>
   <si>
     <t>03_戦闘仕様</t>
@@ -463,10 +463,10 @@
     <t>Ignite/Bleed/Poisonのスタック方式</t>
   </si>
   <si>
-    <t>Poisonは重ね掛け可能で複数スタックのダメージが合算される。Ignite/Bleedは前作(PoE1)では最も強い1つのみが有効だったが、PoE2ではIgniteが複数スタック可能な累積蓄積型DoTへ再設計する。</t>
-  </si>
-  <si>
-    <t>PoE1からの仕様変更点として明記。DoT(No32)の補足詳細。</t>
+    <t xml:space="preserve">Poisonは重ね掛け可能で複数スタックのダメージが合算される。Ignite/Bleedは前作PoE1と同様、同時に複数回付与されても最もダメージの高い1つのみが有効(非累積)であり、この仕様はPoE2でも変更されていない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既存版の誤記(Igniteを多重スタック型と記載していた)を修正。本家PoE2の実際の仕様(最強優先・非スタック)を確認の上訂正(2026-09)。DoT(No32)の補足詳細。</t>
   </si>
   <si>
     <t>04_スキルシステム</t>
@@ -2882,6 +2882,432 @@
   </si>
   <si>
     <t>キャラクター全体に「Fire耐性+X%」を付与するグローバルSuffix。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiritの目安レンジ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ストーリー攻略中盤で数十(目安100前後)、エンドゲーム到達時点で200を超える程度まで、クエスト報酬・装備・パッシブの積み上げで緩やかに上昇する想定とする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiritの主な獲得源(No30)の数値イメージを補足。本家PoE2の実際の到達感を参考に記載。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leech Rate Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1秒あたりのLife/Mana Leech回復量は各最大値の20%、Energy Shieldは10%を上限としてクランプし、瞬間的な全回復を防ぐ(本家PoE2のデフォルト値)。さらに単一Leechインスタンスあたりの回復も、この上限レートの10%までに個別制限される。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leech項目(No50)の具体的な上限値を補足。Web検索で確認した本家PoE2の実際の数値(Life/Mana 20%、ES 10%、インスタンス上限10%)へ訂正(2026-09)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dodge Roll無敵時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dodge Roll発動中は一定の短い時間(目安0.3〜0.5秒程度)を完全無敵とし、無敵終了後もロールモーション終了までは移動速度上昇状態を維持する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dodge/Roll項目(No44)の具体的数値目安を補足。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武器適性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クラス別武器適性マトリクス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warriorは斧/メイス/杖系、Monkはクロー/杖系、Rangerは弓/クロスボウ系、Witch/Sorceressは杖/ワンド系、Mercenaryはクロスボウ系を主軸の適性武器とし、各クラスは適性武器種でのみ使用可能な専用スキルを一部持つ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武器種項目(No74)とクラス項目(No9)を橋渡しする対応関係を明記。既存版で欠落していたクラス-武器の対応付け。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Titan(Warrior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">身体を巨大化させ範囲攻撃・耐久力を極限まで高める重量級Ascendancy。地面を叩き割る巨大武器攻撃や被弾時の反撃効果を得意とする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本家PoE2のAscendancy一覧(No30)の各項目に具体的な特徴づけを追加。パッチで詳細が変わる可能性がある参考情報。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Warbringer(Warrior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">旗(Banner)やコンボ成立時の全体強化を軸に、周囲の敵を巻き込む範囲制圧と味方支援を両立するAscendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本家PoE2参考。パッチで詳細が変わる可能性がある参考情報。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Invoker(Monk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">陰(Cold)と陽(Lightning)2系統のStanceを切り替えながらコンボを繋ぎ、切替直後に強力な追加効果を発動するAscendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Acolyte of Chayula(Monk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">被弾を糧に一時的な無敵状態を得ながらChaosダメージへの変換を活かして攻め続ける、回避特化のリスク・リワード型Ascendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Deadeye(Ranger)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">投射物の貫通・追尾・分裂を極限まで伸ばし、遠距離からの継続射撃で敵を殲滅するAscendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Pathfinder(Ranger)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全Flask効果を常時に近い形で維持し、毒(Poison)蓄積を軸にした持続ダメージで戦うAscendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Infernalist(Witch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自身のLifeを代償に悪魔を召喚し、Fireダメージと共に戦うリスク型のSummoner系Ascendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Blood Mage(Witch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mana主体だった詠唱コストをLife主体へ転換し、強力な呪文を高速で連打できるAscendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Stormweaver(Sorceress)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightning/Coldスキルを交互に使用することで発生する固有バフを重ね、爆発的な呪文火力を生み出すAscendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Chronomancer(Sorceress)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">時間を操作し、被弾直前の状態へ巻き戻す・敵の行動を遅延させる等のユニークな時間操作系Ascendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Witchhunter(Mercenary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">対象に呪い・デバフを蓄積させながらクロスボウで狙撃する、呪術対抗色の強いAscendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Gemling Legionnaire(Mercenary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">装備するSkill Gemの実効Lvやソケット数を底上げし、多数のGemを同時強化して運用するAscendancy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orb of Transmutation的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal(白)装備をMagic(青)へ変化させ、Modを1つ新規付与する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本家PoE2のCurrency構成を参考にした具体例。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orb of Alchemy的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal装備を直接Rare(黄)へ変化させ、複数のModを新規付与する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orb of Augmentation的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic装備の空いているMod枠に1つ追加Modを付与する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regal Orb的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic装備をRareへ格上げし、Mod枠を追加してランダムModを1つ付与する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orb of Annulment的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アイテムに付与済みのランダムなMod1つを除去する。狙ったMod指定はできない諸刃の性質を持つ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orb of Chance的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal装備をランダムなRarityへ変化させる。低確率でUniqueへ変化することがある。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orb of Scouring的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">装備の全Explicit ModをリセットしNormalへ戻す。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artificer’s Orb的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">防具/武器に空きSocketを1つ追加する(装備種別ごとの上限あり)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaal Orb的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不可逆の変質(Corrupt)を付与し、強化/弱体/Rarity固定/破壊のいずれかがランダムに発生する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mirror of Kalandra的アイテム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">対象アイテムの完全な複製を作成する、経済上最高レアリティ帯の通貨。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本家PoE2のCurrency構成を参考にした具体例。極めて低頻度の入手を想定。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キーバインド(実装確定)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">移動キー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W/A/S/Dの4キーで上下左右移動する(MoveUp/MoveDown/MoveLeft/MoveRight)。矢印キーはメニュー操作専用として予約し、キャラクター移動には割り当てない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実装済みのデフォルト値。KeyBindings::ResetToDefaults()準拠。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dodge Roll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spaceキーで発動する(GameAction::Roll)。発動中は短時間の無敵状態になる(No413参照)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スキルスロット1〜5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E(Skill1)/Q(Skill2)/R(Skill3)/V(Skill4)/F(Skill5)の5キーに固定スロットを割り当てる。装着スキル自体はSkill Gem UIでいつでも無コストで付け替え可能。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニュー開閉キー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C=キャラクターシート、I=インベントリ、P=パッシブツリー、K=スキルジェム、B=ベンダー会話(近接時のみ有効)。いずれか1つを開くと他の全メニューは自動的に閉じ、同時に複数のメニューは開けない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キーバインド設定キー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oキーでキーバインド設定画面を開閉する。この画面を開くための割り当て自体は固定でリバインド不可(自分自身を変更すると開けなくなるため)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ベンダーリロール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ベンダー画面を開いている間、Tキーでゴールドを消費して在庫を再抽選する(GameAction::VendorReroll)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メニュー内共通操作(固定・リバインド対象外)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up/Down/Left/Right=カーソル/選択移動、Enter=決定(装備/割当/購入等)、Backspace=respec(パッシブツリーのみ、Orb of Regret消費)、X=売却(インベントリ)、Delete=破棄(インベントリ)。全メニューで共通の固定キーとして扱い、リバインド対象のGameActionには含めない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仕様上の意図的な設計方針(AI/DECISIONS.md参照)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キーバインド設定画面の操作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up/Downでリバインド対象アクションを選択しEnterで割当待機状態に入り、次に押した任意キーをそのアクションへ割り当てる。Escapeで割当待機をキャンセルできる。既に他アクションで使用中のキーやメニュー固定キー(Up/Down/Left/Right/Enter/Backspace/X/Delete)への割当は拒否する。設定は`keybinds.cfg`へ自動保存され次回起動時に復元される。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マウス操作(実装確定)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パッシブツリーのノード選択</t>
+  </si>
+  <si>
+    <t xml:space="preserve">左クリックでツリー上のノード(半径10px、開始ノードのみ12px、判定は当たり判定+6pxの余裕を持たせる)を直接選択する。矢印キーでの選択移動は廃止済み。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09時点で唯一マウスクリック操作を持つパネル。他の全パネルはキーボードのみで操作する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パッシブツリーのConfirm/Cancelボタン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パネル下部に150x36pxのボタンを2つ(間隔24px)横並びで配置する。Confirmクリックで選択中ノードの割り振りを確定し(Enterキーの旧挙動と同一)、Cancelクリックでパネルを閉じる。ボタンはホバー時に色が明るくなる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スキルの照準/発動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マウスカーソル位置(ワールド座標変換後)を照準方向として、キー入力で発動する投射物/範囲スキルの向きを決定する。マウスクリック自体でスキルを発動する操作は持たない(発動は全てキーボードのスキルスロットキー経由)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ウィンドウ/画面仕様(実装確定)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解像度・フレームレート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">解像度1280x720固定(可変解像度・ウィンドウリサイズ非対応)、フレームレート上限120fps。実際の描画は1280x720のRenderTextureへ一旦描画し、等倍スケールでウィンドウへ転写する構成とする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programs/System/Config/Config.h準拠。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUDレイアウト(実装確定)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP/MPオーブ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">半径45pxの円形ゲージを画面下部左右に配置する(HPは左下・赤系、MPは右下・青系、共にY座標は画面下端から80px)。液面の高さで残量比率を表現し、中央に現在値/最大値、下部にラベルを表示する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スキルバー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面下部中央に50x50pxのスロットを横並びで6個配置する(Dodge Roll用1枠+スキル5枠)。Rollスロットとスキル5枠の間は20pxの余白、スキル枠同士は8px間隔とする。各スロット上部にバインドキー名を表示し、クールダウン中は残り時間の割合に応じた高さの半透明黒オーバーレイと秒数テキストを重ねて表示する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デバフアイコン列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPオーブ付近(画面下端から140px上、X=160起点)に28x28pxのアイコンを6px間隔で横に並べる。Ignite/Bleed/Poison/Chill/Freeze/Shock/Stunの発生中のもののみ3文字略称(IGN/BLD/PSN/CHL/FRZ/SHK/STN)と残り時間を表示する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステータステキスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面左上(10,10)にLv/XP(現在値/次レベル必要値)/STR/DEX/INTを常時テキスト表示する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">モーダルパネル共通仕様(実装確定)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パネルサイズ・配置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キャラクターシート/インベントリ/ベンダー/スキルジェムは幅620x480px、パッシブツリーのみ幅700x650px(ツリー表示領域560px+フッター90px)で、いずれも画面中央に配置する。背景色RGBA(15,15,20,235)+アウトライン(RGB 150,150,160、太さ2px)で統一する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">排他制御とポーズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上記いずれかのパネル、またはキーバインド設定画面を開くと他の全パネルを自動的に閉じ、同時に複数開くことはできない。いずれかが開いている間は敵AI・移動・物理演算・当たり判定・アイテム取得・ボスフェーズ等ワールドシミュレーションを一時停止し、パネル自体の操作(UI入力)のみ受け付ける。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既存のNo7(死亡時処理)等と異なりメニュー起因の一時停止として新規に明記。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Smith of Kitava(Warrior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">巨大な鎚を用いた広範囲の物理/Fire複合攻撃と、防具の重さを活かした耐久強化を軸にするAscendancy(Dawn of the Hunt追加)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本家PoE2参考(2026-09時点)。パッチで詳細が変わる可能性がある参考情報。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Martial Artist(Monk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武器を持たない徒手空拳の連続コンボに特化し、素早い連打とコンボ継続で火力を積み上げるAscendancy(Return of the Ancients追加)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Lich(Witch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自身のLifeを闇の力に変換し、Chaosダメージと自己犠牲的な強化を軸に戦うAscendancy(Dawn of the Hunt追加)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ascendancy詳細: Tactician(Mercenary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設置物やサポート火力を軸に、仲間(または自身のミニオン/装置)との連携で戦線を維持するAscendancy(Dawn of the Hunt追加)。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huntressクラス(参考)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spear(片手武器、Str/Dex要求)とBuckler(小型盾)を主軸とし、近接と投擲(遠距離)を1本の武器でシームレスに使い分けるハイブリッド近接クラス。Ascendancyは Ritualist/Amazon/Spirit Walker の3種。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本家PoE2で"Dawn of the Hunt"(2025年4月)にて追加された7クラス目。クラス項目(No9)の訂正内容を補足。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PvP方針</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本家PoE2同様、PvP(対人戦)はコアコンテンツと位置付けず、PvE(対モンスター戦)中心の設計を基本方針とする。専用アリーナ等の対人コンテンツは現時点の本仕様の対象外とし、将来的な検討事項とする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既存版・追加版ともにPvPへの言及が無かったため、方針として明記。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コントローラー操作(参考)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スティック/ボタン割当の基本方針</t>
+  </si>
+  <si>
+    <t xml:space="preserve">左スティック=移動、右スティック=照準(オートターゲット併用可能)、L1/R1等のショルダーボタンにスキルスロット、L2/R2にRoll等の主要アクションを割り当てる。詳細なボタンマップは本家PoE2のController UIを参考に別途策定する。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既存のController UI項目(No328)の補足。現行のC++/SFML実装はキーボード/マウス専用でコントローラー入力は未実装。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実装状況</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実装状況(2026-09時点)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在のC++/SFML実装は、本カテゴリが定義するUncut Skill/Support Gem・Gem経験値/Lv・Quality・Spiritリソースを持たない。実際にはSkillGemData(固定の名前付き8種)を5スロットへ無コストかつ何度でも自由に付け替えるだけの簡易システムである。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仕様書と実装の乖離を明記。今後の実装拡張時の差分把握用。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在のC++/SFML実装は、本カテゴリが定義するAscendancy・Ascendancy専用パッシブツリー・Trial of the Sekhemas等のルーグライク試練を持たない。実際には全クラス共通の単一パッシブツリー(PassiveTreeData)のみ実装済みで、Ascendancy自体が存在しない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仕様書と実装の乖離を明記。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在のC++/SFML実装は、本カテゴリが定義する武器セットA/B切替・Charm・Jewelを持たない。実際には9スロット固定装備+Prefix/Suffix affix+レアリティ4段階(EquipmentSystem)のみ実装済みである。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在のC++/SFML実装は完全ローカル・シングルプレイヤーであり、本カテゴリが定義するパーティ/協力プレイ/ドロップ共有等のマルチプレイ機能は一切実装されていない。本カテゴリは将来のオンライン化を見据えた本家PoE2準拠の設計方針として記載している。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在のC++/SFML実装はアカウント認証・サーバーインスタンス・チャット等を一切持たないスタンドアロン実行ファイルである。本カテゴリの内容は将来オンライン化する場合の設計方針として記載している。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在のC++/SFML実装はCampaignManager::SaveToDisk/LoadFromDiskによるローカルファイル保存のみを行う。本カテゴリが定義するサーバー側永続化・League別分離管理・Cross-Save等は未実装である。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在のC++/SFML実装は課金・アカウント基盤・MTX・Stashタブ購入等を一切持たない。本カテゴリは将来商用展開する場合の設計方針として記載している。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状態異常耐性Charm例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一定時間、Freeze/Chill/Shock等の特定状態異常を無効化するCharm。Flaskと同様にCharge制で使用回数を得る。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本家PoE2のCharm枠(既存のNo110)を参考にした具体例。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">即時回復Charm例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使用時にLifeを瞬時に一定量回復するCharm。Flaskと役割は近いが専用スロットを消費し、Flaskとは独立してCharge/使用回数を管理する。</t>
   </si>
 </sst>
 </file>
@@ -3304,7 +3730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21598642-ADD6-49AB-8A70-AACAEBDDCD67}">
-  <dimension ref="A1:F411"/>
+  <dimension ref="A1:F460"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -10184,8 +10610,942 @@
       </c>
       <c r="F411" s="3"/>
     </row>
+    <row r="412" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A412" s="2">
+        <v>411</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="E412" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="F412" s="3" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A413" s="2">
+        <v>412</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D413" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="E413" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="F413" s="3" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A414" s="2">
+        <v>413</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C414" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D414" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="E414" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="F414" s="3" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A415" s="2">
+        <v>414</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="D415" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="E415" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="F415" s="3" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A416" s="2">
+        <v>415</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="E416" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="F416" s="3" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A417" s="2">
+        <v>416</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="E417" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="F417" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A418" s="2">
+        <v>417</v>
+      </c>
+      <c r="B418" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D418" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="E418" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="F418" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A419" s="2">
+        <v>418</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D419" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="E419" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="F419" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A420" s="2">
+        <v>419</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="E420" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="F420" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A421" s="2">
+        <v>420</v>
+      </c>
+      <c r="B421" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C421" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="E421" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="F421" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A422" s="2">
+        <v>421</v>
+      </c>
+      <c r="B422" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C422" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="E422" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="F422" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A423" s="2">
+        <v>422</v>
+      </c>
+      <c r="B423" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C423" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D423" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="E423" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="F423" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A424" s="2">
+        <v>423</v>
+      </c>
+      <c r="B424" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C424" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D424" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="E424" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="F424" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A425" s="2">
+        <v>424</v>
+      </c>
+      <c r="B425" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="E425" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="F425" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A426" s="2">
+        <v>425</v>
+      </c>
+      <c r="B426" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C426" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D426" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="E426" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="F426" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A427" s="2">
+        <v>426</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D427" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="E427" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="F427" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A428" s="2">
+        <v>427</v>
+      </c>
+      <c r="B428" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C428" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D428" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E428" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F428" s="3" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A429" s="2">
+        <v>428</v>
+      </c>
+      <c r="B429" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C429" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D429" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E429" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F429" s="3"/>
+    </row>
+    <row r="430" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A430" s="2">
+        <v>429</v>
+      </c>
+      <c r="B430" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C430" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E430" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F430" s="3"/>
+    </row>
+    <row r="431" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A431" s="2">
+        <v>430</v>
+      </c>
+      <c r="B431" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C431" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E431" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F431" s="3"/>
+    </row>
+    <row r="432" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A432" s="2">
+        <v>431</v>
+      </c>
+      <c r="B432" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C432" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E432" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F432" s="3"/>
+    </row>
+    <row r="433" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A433" s="2">
+        <v>432</v>
+      </c>
+      <c r="B433" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C433" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D433" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E433" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F433" s="3"/>
+    </row>
+    <row r="434" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A434" s="2">
+        <v>433</v>
+      </c>
+      <c r="B434" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C434" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D434" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E434" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F434" s="3" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A435" s="2">
+        <v>434</v>
+      </c>
+      <c r="B435" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D435" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E435" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F435" s="3"/>
+    </row>
+    <row r="436" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A436" s="2">
+        <v>435</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D436" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E436" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F436" s="3" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A437" s="2">
+        <v>436</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C437" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D437" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E437" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F437" s="3"/>
+    </row>
+    <row r="438" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A438" s="2">
+        <v>437</v>
+      </c>
+      <c r="B438" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C438" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D438" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E438" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F438" s="3"/>
+    </row>
+    <row r="439" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A439" s="2">
+        <v>438</v>
+      </c>
+      <c r="B439" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C439" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E439" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F439" s="3" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A440" s="2">
+        <v>439</v>
+      </c>
+      <c r="B440" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C440" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D440" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E440" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F440" s="3"/>
+    </row>
+    <row r="441" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A441" s="2">
+        <v>440</v>
+      </c>
+      <c r="B441" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D441" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E441" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F441" s="3"/>
+    </row>
+    <row r="442" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A442" s="2">
+        <v>441</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C442" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E442" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F442" s="3"/>
+    </row>
+    <row r="443" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A443" s="2">
+        <v>442</v>
+      </c>
+      <c r="B443" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C443" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E443" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F443" s="3"/>
+    </row>
+    <row r="444" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A444" s="2">
+        <v>443</v>
+      </c>
+      <c r="B444" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C444" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E444" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F444" s="3"/>
+    </row>
+    <row r="445" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A445" s="2">
+        <v>444</v>
+      </c>
+      <c r="B445" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C445" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E445" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F445" s="3" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A447" s="2">
+        <v>446</v>
+      </c>
+      <c r="B447" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E447" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F447" s="3" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A448" s="2">
+        <v>447</v>
+      </c>
+      <c r="B448" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C448" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D448" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E448" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F448" s="3" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A449" s="2">
+        <v>448</v>
+      </c>
+      <c r="B449" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C449" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E449" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F449" s="3" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A450" s="2">
+        <v>449</v>
+      </c>
+      <c r="B450" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C450" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D450" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E450" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F450" s="3" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A451" s="2">
+        <v>450</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C451" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D451" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E451" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F451" s="3" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A452" s="2">
+        <v>451</v>
+      </c>
+      <c r="B452" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C452" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D452" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E452" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F452" s="3" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A453" s="2">
+        <v>452</v>
+      </c>
+      <c r="B453" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C453" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D453" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E453" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F453" s="3" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A454" s="2">
+        <v>453</v>
+      </c>
+      <c r="B454" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C454" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D454" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E454" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F454" s="3" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A455" s="2">
+        <v>454</v>
+      </c>
+      <c r="B455" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C455" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D455" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E455" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F455" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A456" s="2">
+        <v>455</v>
+      </c>
+      <c r="B456" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C456" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D456" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E456" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F456" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A457" s="2">
+        <v>456</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D457" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E457" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F457" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A458" s="2">
+        <v>457</v>
+      </c>
+      <c r="B458" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="C458" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D458" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E458" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F458" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A459" s="2">
+        <v>458</v>
+      </c>
+      <c r="B459" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D459" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E459" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F459" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A460" s="2">
+        <v>459</v>
+      </c>
+      <c r="B460" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D460" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E460" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F460" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F411" xr:uid="{21598642-ADD6-49AB-8A70-AACAEBDDCD67}"/>
+  <autoFilter ref="A1:F460" xr:uid="{21598642-ADD6-49AB-8A70-AACAEBDDCD67}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10193,7 +11553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75622AD1-D3B8-4FA3-B036-78041C75B546}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -10447,8 +11807,212 @@
       </c>
       <c r="E16" s="3"/>
     </row>
+    <row r="17" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1085</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E16" xr:uid="{75622AD1-D3B8-4FA3-B036-78041C75B546}"/>
+  <autoFilter ref="A1:E28" xr:uid="{75622AD1-D3B8-4FA3-B036-78041C75B546}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PoE2_仕様書.xlsx
+++ b/PoE2_仕様書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazus\Desktop\POE2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazus\source\repos\企業用\POE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EDACFFE-AAE6-4965-90FA-B81C52938E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B659B398-4E4E-498D-9C68-CD17AC21923A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91AE84DB-8705-4A0B-863F-59311E04910A}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="1088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="1090">
   <si>
     <t>No</t>
   </si>
@@ -133,13 +133,13 @@
     <t>クラス</t>
   </si>
   <si>
-    <t xml:space="preserve">Warrior/Monk/Ranger/Witch/Sorceress/Mercenary/Huntressの7クラスを用意し、各クラスは開始位置・武器適性・スキル傾向が異なる。2026年12月のバージョン1.0で8クラス目Duelist(新武器種Sword対応)が追加予定。</t>
+    <t>Warrior/Monk/Ranger/Witch/Sorceress/Mercenary/Huntressの7クラスを用意し、各クラスは開始位置・武器適性・スキル傾向が異なる。2026年12月のバージョン1.0で8クラス目Duelist(新武器種Sword対応)が追加予定。</t>
   </si>
   <si>
     <t>Ascendancy</t>
   </si>
   <si>
-    <t xml:space="preserve">各クラスに2〜3種のAscendancy(クラス・バージョンにより数が異なる)を用意し、ルーグライク試練(Trial of the Sekhemas等)のクリア報酬として最大8ポイントを獲得し専用パッシブを解放する。</t>
+    <t>各クラスに2〜3種のAscendancy(クラス・バージョンにより数が異なる)を用意し、ルーグライク試練(Trial of the Sekhemas等)のクリア報酬として最大8ポイントを獲得し専用パッシブを解放する。</t>
   </si>
   <si>
     <t>レベル</t>
@@ -277,10 +277,10 @@
     <t>Ascendancy一覧(参考)</t>
   </si>
   <si>
-    <t xml:space="preserve">Warrior→Titan/Warbringer/Smith of Kitava、Monk→Invoker/Acolyte of Chayula/Martial Artist、Ranger→Deadeye/Pathfinder、Witch→Infernalist/Blood Mage/Lich、Sorceress→Stormweaver/Chronomancer、Mercenary→Witchhunter/Gemling Legionnaire/Tactician、Huntress→Ritualist/Amazon/Spirit Walkerの計19種、7クラス(2026-09時点、Early Access中)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy項目(No8)の具体名称を参考情報として付記。2026-09時点の内容へ更新(Dawn of the Hunt/Return of the Ancientsの追加分を反映)。1.0(2026-12-11予定)でさらに追加・変更の可能性あり。</t>
+    <t>Warrior→Titan/Warbringer/Smith of Kitava、Monk→Invoker/Acolyte of Chayula/Martial Artist、Ranger→Deadeye/Pathfinder、Witch→Infernalist/Blood Mage/Lich、Sorceress→Stormweaver/Chronomancer、Mercenary→Witchhunter/Gemling Legionnaire/Tactician、Huntress→Ritualist/Amazon/Spirit Walkerの計19種、7クラス(2026-09時点、Early Access中)。</t>
+  </si>
+  <si>
+    <t>Ascendancy項目(No8)の具体名称を参考情報として付記。2026-09時点の内容へ更新(Dawn of the Hunt/Return of the Ancientsの追加分を反映)。1.0(2026-12-11予定)でさらに追加・変更の可能性あり。</t>
   </si>
   <si>
     <t>03_戦闘仕様</t>
@@ -463,10 +463,10 @@
     <t>Ignite/Bleed/Poisonのスタック方式</t>
   </si>
   <si>
-    <t xml:space="preserve">Poisonは重ね掛け可能で複数スタックのダメージが合算される。Ignite/Bleedは前作PoE1と同様、同時に複数回付与されても最もダメージの高い1つのみが有効(非累積)であり、この仕様はPoE2でも変更されていない。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存版の誤記(Igniteを多重スタック型と記載していた)を修正。本家PoE2の実際の仕様(最強優先・非スタック)を確認の上訂正(2026-09)。DoT(No32)の補足詳細。</t>
+    <t>Poisonは重ね掛け可能で複数スタックのダメージが合算される。Ignite/Bleedは前作PoE1と同様、同時に複数回付与されても最もダメージの高い1つのみが有効(非累積)であり、この仕様はPoE2でも変更されていない。</t>
+  </si>
+  <si>
+    <t>既存版の誤記(Igniteを多重スタック型と記載していた)を修正。本家PoE2の実際の仕様(最強優先・非スタック)を確認の上訂正(2026-09)。DoT(No32)の補足詳細。</t>
   </si>
   <si>
     <t>04_スキルシステム</t>
@@ -2884,430 +2884,436 @@
     <t>キャラクター全体に「Fire耐性+X%」を付与するグローバルSuffix。</t>
   </si>
   <si>
-    <t xml:space="preserve">Spiritの目安レンジ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ストーリー攻略中盤で数十(目安100前後)、エンドゲーム到達時点で200を超える程度まで、クエスト報酬・装備・パッシブの積み上げで緩やかに上昇する想定とする。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spiritの主な獲得源(No30)の数値イメージを補足。本家PoE2の実際の到達感を参考に記載。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leech Rate Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1秒あたりのLife/Mana Leech回復量は各最大値の20%、Energy Shieldは10%を上限としてクランプし、瞬間的な全回復を防ぐ(本家PoE2のデフォルト値)。さらに単一Leechインスタンスあたりの回復も、この上限レートの10%までに個別制限される。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leech項目(No50)の具体的な上限値を補足。Web検索で確認した本家PoE2の実際の数値(Life/Mana 20%、ES 10%、インスタンス上限10%)へ訂正(2026-09)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dodge Roll無敵時間</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dodge Roll発動中は一定の短い時間(目安0.3〜0.5秒程度)を完全無敵とし、無敵終了後もロールモーション終了までは移動速度上昇状態を維持する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dodge/Roll項目(No44)の具体的数値目安を補足。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">武器適性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">クラス別武器適性マトリクス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warriorは斧/メイス/杖系、Monkはクロー/杖系、Rangerは弓/クロスボウ系、Witch/Sorceressは杖/ワンド系、Mercenaryはクロスボウ系を主軸の適性武器とし、各クラスは適性武器種でのみ使用可能な専用スキルを一部持つ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">武器種項目(No74)とクラス項目(No9)を橋渡しする対応関係を明記。既存版で欠落していたクラス-武器の対応付け。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Titan(Warrior)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">身体を巨大化させ範囲攻撃・耐久力を極限まで高める重量級Ascendancy。地面を叩き割る巨大武器攻撃や被弾時の反撃効果を得意とする。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本家PoE2のAscendancy一覧(No30)の各項目に具体的な特徴づけを追加。パッチで詳細が変わる可能性がある参考情報。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Warbringer(Warrior)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">旗(Banner)やコンボ成立時の全体強化を軸に、周囲の敵を巻き込む範囲制圧と味方支援を両立するAscendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本家PoE2参考。パッチで詳細が変わる可能性がある参考情報。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Invoker(Monk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陰(Cold)と陽(Lightning)2系統のStanceを切り替えながらコンボを繋ぎ、切替直後に強力な追加効果を発動するAscendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Acolyte of Chayula(Monk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">被弾を糧に一時的な無敵状態を得ながらChaosダメージへの変換を活かして攻め続ける、回避特化のリスク・リワード型Ascendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Deadeye(Ranger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">投射物の貫通・追尾・分裂を極限まで伸ばし、遠距離からの継続射撃で敵を殲滅するAscendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Pathfinder(Ranger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全Flask効果を常時に近い形で維持し、毒(Poison)蓄積を軸にした持続ダメージで戦うAscendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Infernalist(Witch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自身のLifeを代償に悪魔を召喚し、Fireダメージと共に戦うリスク型のSummoner系Ascendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Blood Mage(Witch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mana主体だった詠唱コストをLife主体へ転換し、強力な呪文を高速で連打できるAscendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Stormweaver(Sorceress)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightning/Coldスキルを交互に使用することで発生する固有バフを重ね、爆発的な呪文火力を生み出すAscendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Chronomancer(Sorceress)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">時間を操作し、被弾直前の状態へ巻き戻す・敵の行動を遅延させる等のユニークな時間操作系Ascendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Witchhunter(Mercenary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">対象に呪い・デバフを蓄積させながらクロスボウで狙撃する、呪術対抗色の強いAscendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Gemling Legionnaire(Mercenary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">装備するSkill Gemの実効Lvやソケット数を底上げし、多数のGemを同時強化して運用するAscendancy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orb of Transmutation的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal(白)装備をMagic(青)へ変化させ、Modを1つ新規付与する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本家PoE2のCurrency構成を参考にした具体例。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orb of Alchemy的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal装備を直接Rare(黄)へ変化させ、複数のModを新規付与する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orb of Augmentation的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic装備の空いているMod枠に1つ追加Modを付与する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regal Orb的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic装備をRareへ格上げし、Mod枠を追加してランダムModを1つ付与する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orb of Annulment的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アイテムに付与済みのランダムなMod1つを除去する。狙ったMod指定はできない諸刃の性質を持つ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orb of Chance的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal装備をランダムなRarityへ変化させる。低確率でUniqueへ変化することがある。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orb of Scouring的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">装備の全Explicit ModをリセットしNormalへ戻す。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artificer’s Orb的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">防具/武器に空きSocketを1つ追加する(装備種別ごとの上限あり)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaal Orb的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不可逆の変質(Corrupt)を付与し、強化/弱体/Rarity固定/破壊のいずれかがランダムに発生する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mirror of Kalandra的アイテム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">対象アイテムの完全な複製を作成する、経済上最高レアリティ帯の通貨。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本家PoE2のCurrency構成を参考にした具体例。極めて低頻度の入手を想定。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キーバインド(実装確定)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">移動キー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W/A/S/Dの4キーで上下左右移動する(MoveUp/MoveDown/MoveLeft/MoveRight)。矢印キーはメニュー操作専用として予約し、キャラクター移動には割り当てない。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">実装済みのデフォルト値。KeyBindings::ResetToDefaults()準拠。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dodge Roll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spaceキーで発動する(GameAction::Roll)。発動中は短時間の無敵状態になる(No413参照)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スキルスロット1〜5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E(Skill1)/Q(Skill2)/R(Skill3)/V(Skill4)/F(Skill5)の5キーに固定スロットを割り当てる。装着スキル自体はSkill Gem UIでいつでも無コストで付け替え可能。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メニュー開閉キー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C=キャラクターシート、I=インベントリ、P=パッシブツリー、K=スキルジェム、B=ベンダー会話(近接時のみ有効)。いずれか1つを開くと他の全メニューは自動的に閉じ、同時に複数のメニューは開けない。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キーバインド設定キー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oキーでキーバインド設定画面を開閉する。この画面を開くための割り当て自体は固定でリバインド不可(自分自身を変更すると開けなくなるため)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ベンダーリロール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ベンダー画面を開いている間、Tキーでゴールドを消費して在庫を再抽選する(GameAction::VendorReroll)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メニュー内共通操作(固定・リバインド対象外)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up/Down/Left/Right=カーソル/選択移動、Enter=決定(装備/割当/購入等)、Backspace=respec(パッシブツリーのみ、Orb of Regret消費)、X=売却(インベントリ)、Delete=破棄(インベントリ)。全メニューで共通の固定キーとして扱い、リバインド対象のGameActionには含めない。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仕様上の意図的な設計方針(AI/DECISIONS.md参照)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キーバインド設定画面の操作</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up/Downでリバインド対象アクションを選択しEnterで割当待機状態に入り、次に押した任意キーをそのアクションへ割り当てる。Escapeで割当待機をキャンセルできる。既に他アクションで使用中のキーやメニュー固定キー(Up/Down/Left/Right/Enter/Backspace/X/Delete)への割当は拒否する。設定は`keybinds.cfg`へ自動保存され次回起動時に復元される。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マウス操作(実装確定)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パッシブツリーのノード選択</t>
-  </si>
-  <si>
-    <t xml:space="preserve">左クリックでツリー上のノード(半径10px、開始ノードのみ12px、判定は当たり判定+6pxの余裕を持たせる)を直接選択する。矢印キーでの選択移動は廃止済み。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09時点で唯一マウスクリック操作を持つパネル。他の全パネルはキーボードのみで操作する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パッシブツリーのConfirm/Cancelボタン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パネル下部に150x36pxのボタンを2つ(間隔24px)横並びで配置する。Confirmクリックで選択中ノードの割り振りを確定し(Enterキーの旧挙動と同一)、Cancelクリックでパネルを閉じる。ボタンはホバー時に色が明るくなる。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スキルの照準/発動</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マウスカーソル位置(ワールド座標変換後)を照準方向として、キー入力で発動する投射物/範囲スキルの向きを決定する。マウスクリック自体でスキルを発動する操作は持たない(発動は全てキーボードのスキルスロットキー経由)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ウィンドウ/画面仕様(実装確定)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">解像度・フレームレート</t>
-  </si>
-  <si>
-    <t xml:space="preserve">解像度1280x720固定(可変解像度・ウィンドウリサイズ非対応)、フレームレート上限120fps。実際の描画は1280x720のRenderTextureへ一旦描画し、等倍スケールでウィンドウへ転写する構成とする。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programs/System/Config/Config.h準拠。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUDレイアウト(実装確定)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP/MPオーブ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">半径45pxの円形ゲージを画面下部左右に配置する(HPは左下・赤系、MPは右下・青系、共にY座標は画面下端から80px)。液面の高さで残量比率を表現し、中央に現在値/最大値、下部にラベルを表示する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スキルバー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">画面下部中央に50x50pxのスロットを横並びで6個配置する(Dodge Roll用1枠+スキル5枠)。Rollスロットとスキル5枠の間は20pxの余白、スキル枠同士は8px間隔とする。各スロット上部にバインドキー名を表示し、クールダウン中は残り時間の割合に応じた高さの半透明黒オーバーレイと秒数テキストを重ねて表示する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デバフアイコン列</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPオーブ付近(画面下端から140px上、X=160起点)に28x28pxのアイコンを6px間隔で横に並べる。Ignite/Bleed/Poison/Chill/Freeze/Shock/Stunの発生中のもののみ3文字略称(IGN/BLD/PSN/CHL/FRZ/SHK/STN)と残り時間を表示する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ステータステキスト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">画面左上(10,10)にLv/XP(現在値/次レベル必要値)/STR/DEX/INTを常時テキスト表示する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">モーダルパネル共通仕様(実装確定)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パネルサイズ・配置</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キャラクターシート/インベントリ/ベンダー/スキルジェムは幅620x480px、パッシブツリーのみ幅700x650px(ツリー表示領域560px+フッター90px)で、いずれも画面中央に配置する。背景色RGBA(15,15,20,235)+アウトライン(RGB 150,150,160、太さ2px)で統一する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">排他制御とポーズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上記いずれかのパネル、またはキーバインド設定画面を開くと他の全パネルを自動的に閉じ、同時に複数開くことはできない。いずれかが開いている間は敵AI・移動・物理演算・当たり判定・アイテム取得・ボスフェーズ等ワールドシミュレーションを一時停止し、パネル自体の操作(UI入力)のみ受け付ける。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存のNo7(死亡時処理)等と異なりメニュー起因の一時停止として新規に明記。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Smith of Kitava(Warrior)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">巨大な鎚を用いた広範囲の物理/Fire複合攻撃と、防具の重さを活かした耐久強化を軸にするAscendancy(Dawn of the Hunt追加)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本家PoE2参考(2026-09時点)。パッチで詳細が変わる可能性がある参考情報。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Martial Artist(Monk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">武器を持たない徒手空拳の連続コンボに特化し、素早い連打とコンボ継続で火力を積み上げるAscendancy(Return of the Ancients追加)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Lich(Witch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自身のLifeを闇の力に変換し、Chaosダメージと自己犠牲的な強化を軸に戦うAscendancy(Dawn of the Hunt追加)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascendancy詳細: Tactician(Mercenary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">設置物やサポート火力を軸に、仲間(または自身のミニオン/装置)との連携で戦線を維持するAscendancy(Dawn of the Hunt追加)。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huntressクラス(参考)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spear(片手武器、Str/Dex要求)とBuckler(小型盾)を主軸とし、近接と投擲(遠距離)を1本の武器でシームレスに使い分けるハイブリッド近接クラス。Ascendancyは Ritualist/Amazon/Spirit Walker の3種。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本家PoE2で"Dawn of the Hunt"(2025年4月)にて追加された7クラス目。クラス項目(No9)の訂正内容を補足。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PvP方針</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本家PoE2同様、PvP(対人戦)はコアコンテンツと位置付けず、PvE(対モンスター戦)中心の設計を基本方針とする。専用アリーナ等の対人コンテンツは現時点の本仕様の対象外とし、将来的な検討事項とする。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存版・追加版ともにPvPへの言及が無かったため、方針として明記。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コントローラー操作(参考)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スティック/ボタン割当の基本方針</t>
-  </si>
-  <si>
-    <t xml:space="preserve">左スティック=移動、右スティック=照準(オートターゲット併用可能)、L1/R1等のショルダーボタンにスキルスロット、L2/R2にRoll等の主要アクションを割り当てる。詳細なボタンマップは本家PoE2のController UIを参考に別途策定する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存のController UI項目(No328)の補足。現行のC++/SFML実装はキーボード/マウス専用でコントローラー入力は未実装。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">実装状況</t>
-  </si>
-  <si>
-    <t xml:space="preserve">実装状況(2026-09時点)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在のC++/SFML実装は、本カテゴリが定義するUncut Skill/Support Gem・Gem経験値/Lv・Quality・Spiritリソースを持たない。実際にはSkillGemData(固定の名前付き8種)を5スロットへ無コストかつ何度でも自由に付け替えるだけの簡易システムである。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仕様書と実装の乖離を明記。今後の実装拡張時の差分把握用。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在のC++/SFML実装は、本カテゴリが定義するAscendancy・Ascendancy専用パッシブツリー・Trial of the Sekhemas等のルーグライク試練を持たない。実際には全クラス共通の単一パッシブツリー(PassiveTreeData)のみ実装済みで、Ascendancy自体が存在しない。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仕様書と実装の乖離を明記。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在のC++/SFML実装は、本カテゴリが定義する武器セットA/B切替・Charm・Jewelを持たない。実際には9スロット固定装備+Prefix/Suffix affix+レアリティ4段階(EquipmentSystem)のみ実装済みである。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在のC++/SFML実装は完全ローカル・シングルプレイヤーであり、本カテゴリが定義するパーティ/協力プレイ/ドロップ共有等のマルチプレイ機能は一切実装されていない。本カテゴリは将来のオンライン化を見据えた本家PoE2準拠の設計方針として記載している。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在のC++/SFML実装はアカウント認証・サーバーインスタンス・チャット等を一切持たないスタンドアロン実行ファイルである。本カテゴリの内容は将来オンライン化する場合の設計方針として記載している。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在のC++/SFML実装はCampaignManager::SaveToDisk/LoadFromDiskによるローカルファイル保存のみを行う。本カテゴリが定義するサーバー側永続化・League別分離管理・Cross-Save等は未実装である。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在のC++/SFML実装は課金・アカウント基盤・MTX・Stashタブ購入等を一切持たない。本カテゴリは将来商用展開する場合の設計方針として記載している。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状態異常耐性Charm例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一定時間、Freeze/Chill/Shock等の特定状態異常を無効化するCharm。Flaskと同様にCharge制で使用回数を得る。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本家PoE2のCharm枠(既存のNo110)を参考にした具体例。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">即時回復Charm例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">使用時にLifeを瞬時に一定量回復するCharm。Flaskと役割は近いが専用スロットを消費し、Flaskとは独立してCharge/使用回数を管理する。</t>
+    <t>Spiritの目安レンジ</t>
+  </si>
+  <si>
+    <t>ストーリー攻略中盤で数十(目安100前後)、エンドゲーム到達時点で200を超える程度まで、クエスト報酬・装備・パッシブの積み上げで緩やかに上昇する想定とする。</t>
+  </si>
+  <si>
+    <t>Spiritの主な獲得源(No30)の数値イメージを補足。本家PoE2の実際の到達感を参考に記載。</t>
+  </si>
+  <si>
+    <t>Leech Rate Cap</t>
+  </si>
+  <si>
+    <t>1秒あたりのLife/Mana Leech回復量は各最大値の20%、Energy Shieldは10%を上限としてクランプし、瞬間的な全回復を防ぐ(本家PoE2のデフォルト値)。さらに単一Leechインスタンスあたりの回復も、この上限レートの10%までに個別制限される。</t>
+  </si>
+  <si>
+    <t>Leech項目(No50)の具体的な上限値を補足。Web検索で確認した本家PoE2の実際の数値(Life/Mana 20%、ES 10%、インスタンス上限10%)へ訂正(2026-09)。</t>
+  </si>
+  <si>
+    <t>Dodge Roll無敵時間</t>
+  </si>
+  <si>
+    <t>Dodge Roll発動中は一定の短い時間(目安0.3〜0.5秒程度)を完全無敵とし、無敵終了後もロールモーション終了までは移動速度上昇状態を維持する。</t>
+  </si>
+  <si>
+    <t>Dodge/Roll項目(No44)の具体的数値目安を補足。</t>
+  </si>
+  <si>
+    <t>武器適性</t>
+  </si>
+  <si>
+    <t>クラス別武器適性マトリクス</t>
+  </si>
+  <si>
+    <t>Warriorは斧/メイス/杖系、Monkはクロー/杖系、Rangerは弓/クロスボウ系、Witch/Sorceressは杖/ワンド系、Mercenaryはクロスボウ系を主軸の適性武器とし、各クラスは適性武器種でのみ使用可能な専用スキルを一部持つ。</t>
+  </si>
+  <si>
+    <t>武器種項目(No74)とクラス項目(No9)を橋渡しする対応関係を明記。既存版で欠落していたクラス-武器の対応付け。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Titan(Warrior)</t>
+  </si>
+  <si>
+    <t>身体を巨大化させ範囲攻撃・耐久力を極限まで高める重量級Ascendancy。地面を叩き割る巨大武器攻撃や被弾時の反撃効果を得意とする。</t>
+  </si>
+  <si>
+    <t>本家PoE2のAscendancy一覧(No30)の各項目に具体的な特徴づけを追加。パッチで詳細が変わる可能性がある参考情報。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Warbringer(Warrior)</t>
+  </si>
+  <si>
+    <t>旗(Banner)やコンボ成立時の全体強化を軸に、周囲の敵を巻き込む範囲制圧と味方支援を両立するAscendancy。</t>
+  </si>
+  <si>
+    <t>本家PoE2参考。パッチで詳細が変わる可能性がある参考情報。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Invoker(Monk)</t>
+  </si>
+  <si>
+    <t>陰(Cold)と陽(Lightning)2系統のStanceを切り替えながらコンボを繋ぎ、切替直後に強力な追加効果を発動するAscendancy。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Acolyte of Chayula(Monk)</t>
+  </si>
+  <si>
+    <t>被弾を糧に一時的な無敵状態を得ながらChaosダメージへの変換を活かして攻め続ける、回避特化のリスク・リワード型Ascendancy。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Deadeye(Ranger)</t>
+  </si>
+  <si>
+    <t>投射物の貫通・追尾・分裂を極限まで伸ばし、遠距離からの継続射撃で敵を殲滅するAscendancy。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Pathfinder(Ranger)</t>
+  </si>
+  <si>
+    <t>全Flask効果を常時に近い形で維持し、毒(Poison)蓄積を軸にした持続ダメージで戦うAscendancy。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Infernalist(Witch)</t>
+  </si>
+  <si>
+    <t>自身のLifeを代償に悪魔を召喚し、Fireダメージと共に戦うリスク型のSummoner系Ascendancy。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Blood Mage(Witch)</t>
+  </si>
+  <si>
+    <t>Mana主体だった詠唱コストをLife主体へ転換し、強力な呪文を高速で連打できるAscendancy。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Stormweaver(Sorceress)</t>
+  </si>
+  <si>
+    <t>Lightning/Coldスキルを交互に使用することで発生する固有バフを重ね、爆発的な呪文火力を生み出すAscendancy。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Chronomancer(Sorceress)</t>
+  </si>
+  <si>
+    <t>時間を操作し、被弾直前の状態へ巻き戻す・敵の行動を遅延させる等のユニークな時間操作系Ascendancy。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Witchhunter(Mercenary)</t>
+  </si>
+  <si>
+    <t>対象に呪い・デバフを蓄積させながらクロスボウで狙撃する、呪術対抗色の強いAscendancy。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Gemling Legionnaire(Mercenary)</t>
+  </si>
+  <si>
+    <t>装備するSkill Gemの実効Lvやソケット数を底上げし、多数のGemを同時強化して運用するAscendancy。</t>
+  </si>
+  <si>
+    <t>Orb of Transmutation的アイテム</t>
+  </si>
+  <si>
+    <t>Normal(白)装備をMagic(青)へ変化させ、Modを1つ新規付与する。</t>
+  </si>
+  <si>
+    <t>本家PoE2のCurrency構成を参考にした具体例。</t>
+  </si>
+  <si>
+    <t>Orb of Alchemy的アイテム</t>
+  </si>
+  <si>
+    <t>Normal装備を直接Rare(黄)へ変化させ、複数のModを新規付与する。</t>
+  </si>
+  <si>
+    <t>Orb of Augmentation的アイテム</t>
+  </si>
+  <si>
+    <t>Magic装備の空いているMod枠に1つ追加Modを付与する。</t>
+  </si>
+  <si>
+    <t>Regal Orb的アイテム</t>
+  </si>
+  <si>
+    <t>Magic装備をRareへ格上げし、Mod枠を追加してランダムModを1つ付与する。</t>
+  </si>
+  <si>
+    <t>Orb of Annulment的アイテム</t>
+  </si>
+  <si>
+    <t>アイテムに付与済みのランダムなMod1つを除去する。狙ったMod指定はできない諸刃の性質を持つ。</t>
+  </si>
+  <si>
+    <t>Orb of Chance的アイテム</t>
+  </si>
+  <si>
+    <t>Normal装備をランダムなRarityへ変化させる。低確率でUniqueへ変化することがある。</t>
+  </si>
+  <si>
+    <t>Orb of Scouring的アイテム</t>
+  </si>
+  <si>
+    <t>装備の全Explicit ModをリセットしNormalへ戻す。</t>
+  </si>
+  <si>
+    <t>Artificer’s Orb的アイテム</t>
+  </si>
+  <si>
+    <t>防具/武器に空きSocketを1つ追加する(装備種別ごとの上限あり)。</t>
+  </si>
+  <si>
+    <t>Vaal Orb的アイテム</t>
+  </si>
+  <si>
+    <t>不可逆の変質(Corrupt)を付与し、強化/弱体/Rarity固定/破壊のいずれかがランダムに発生する。</t>
+  </si>
+  <si>
+    <t>Mirror of Kalandra的アイテム</t>
+  </si>
+  <si>
+    <t>対象アイテムの完全な複製を作成する、経済上最高レアリティ帯の通貨。</t>
+  </si>
+  <si>
+    <t>本家PoE2のCurrency構成を参考にした具体例。極めて低頻度の入手を想定。</t>
+  </si>
+  <si>
+    <t>キーバインド(実装確定)</t>
+  </si>
+  <si>
+    <t>移動キー</t>
+  </si>
+  <si>
+    <t>W/A/S/Dの4キーで上下左右移動する(MoveUp/MoveDown/MoveLeft/MoveRight)。矢印キーはメニュー操作専用として予約し、キャラクター移動には割り当てない。</t>
+  </si>
+  <si>
+    <t>実装済みのデフォルト値。KeyBindings::ResetToDefaults()準拠。</t>
+  </si>
+  <si>
+    <t>Dodge Roll</t>
+  </si>
+  <si>
+    <t>Spaceキーで発動する(GameAction::Roll)。発動中は短時間の無敵状態になる(No413参照)。</t>
+  </si>
+  <si>
+    <t>スキルスロット1〜5</t>
+  </si>
+  <si>
+    <t>E(Skill1)/Q(Skill2)/R(Skill3)/V(Skill4)/F(Skill5)の5キーに固定スロットを割り当てる。装着スキル自体はSkill Gem UIでいつでも無コストで付け替え可能。</t>
+  </si>
+  <si>
+    <t>メニュー開閉キー</t>
+  </si>
+  <si>
+    <t>C=キャラクターシート、I=インベントリ、P=パッシブツリー、K=スキルジェム、B=ベンダー会話(近接時のみ有効)。いずれか1つを開くと他の全メニューは自動的に閉じ、同時に複数のメニューは開けない。</t>
+  </si>
+  <si>
+    <t>キーバインド設定キー</t>
+  </si>
+  <si>
+    <t>Oキーでキーバインド設定画面を開閉する。この画面を開くための割り当て自体は固定でリバインド不可(自分自身を変更すると開けなくなるため)。</t>
+  </si>
+  <si>
+    <t>ベンダーリロール</t>
+  </si>
+  <si>
+    <t>ベンダー画面を開いている間、Tキーでゴールドを消費して在庫を再抽選する(GameAction::VendorReroll)。</t>
+  </si>
+  <si>
+    <t>メニュー内共通操作(固定・リバインド対象外)</t>
+  </si>
+  <si>
+    <t>Up/Down/Left/Right=カーソル/選択移動、Enter=決定(装備/割当/購入等)、Backspace=respec(パッシブツリーのみ、Orb of Regret消費)、X=売却(インベントリ)、Delete=破棄(インベントリ)。全メニューで共通の固定キーとして扱い、リバインド対象のGameActionには含めない。</t>
+  </si>
+  <si>
+    <t>仕様上の意図的な設計方針(AI/DECISIONS.md参照)。</t>
+  </si>
+  <si>
+    <t>キーバインド設定画面の操作</t>
+  </si>
+  <si>
+    <t>Up/Downでリバインド対象アクションを選択しEnterで割当待機状態に入り、次に押した任意キーをそのアクションへ割り当てる。Escapeで割当待機をキャンセルできる。既に他アクションで使用中のキーやメニュー固定キー(Up/Down/Left/Right/Enter/Backspace/X/Delete)への割当は拒否する。設定は`keybinds.cfg`へ自動保存され次回起動時に復元される。</t>
+  </si>
+  <si>
+    <t>マウス操作(実装確定)</t>
+  </si>
+  <si>
+    <t>パッシブツリーのノード選択</t>
+  </si>
+  <si>
+    <t>左クリックでツリー上のノード(半径10px、開始ノードのみ12px、判定は当たり判定+6pxの余裕を持たせる)を直接選択する。矢印キーでの選択移動は廃止済み。</t>
+  </si>
+  <si>
+    <t>2026-09時点で唯一マウスクリック操作を持つパネル。他の全パネルはキーボードのみで操作する。</t>
+  </si>
+  <si>
+    <t>パッシブツリーのConfirm/Cancelボタン</t>
+  </si>
+  <si>
+    <t>パネル下部に150x36pxのボタンを2つ(間隔24px)横並びで配置する。Confirmクリックで選択中ノードの割り振りを確定し(Enterキーの旧挙動と同一)、Cancelクリックでパネルを閉じる。ボタンはホバー時に色が明るくなる。</t>
+  </si>
+  <si>
+    <t>スキルの照準/発動</t>
+  </si>
+  <si>
+    <t>マウスカーソル位置(ワールド座標変換後)を照準方向として、キー入力で発動する投射物/範囲スキルの向きを決定する。マウスクリック自体でスキルを発動する操作は持たない(発動は全てキーボードのスキルスロットキー経由)。</t>
+  </si>
+  <si>
+    <t>ウィンドウ/画面仕様(実装確定)</t>
+  </si>
+  <si>
+    <t>解像度・フレームレート</t>
+  </si>
+  <si>
+    <t>解像度1280x720固定(可変解像度・ウィンドウリサイズ非対応)、フレームレート上限120fps。実際の描画は1280x720のRenderTextureへ一旦描画し、等倍スケールでウィンドウへ転写する構成とする。</t>
+  </si>
+  <si>
+    <t>Programs/System/Config/Config.h準拠。</t>
+  </si>
+  <si>
+    <t>HUDレイアウト(実装確定)</t>
+  </si>
+  <si>
+    <t>HP/MPオーブ</t>
+  </si>
+  <si>
+    <t>半径45pxの円形ゲージを画面下部左右に配置する(HPは左下・赤系、MPは右下・青系、共にY座標は画面下端から80px)。液面の高さで残量比率を表現し、中央に現在値/最大値、下部にラベルを表示する。</t>
+  </si>
+  <si>
+    <t>スキルバー</t>
+  </si>
+  <si>
+    <t>画面下部中央に50x50pxのスロットを横並びで6個配置する(Dodge Roll用1枠+スキル5枠)。Rollスロットとスキル5枠の間は20pxの余白、スキル枠同士は8px間隔とする。各スロット上部にバインドキー名を表示し、クールダウン中は残り時間の割合に応じた高さの半透明黒オーバーレイと秒数テキストを重ねて表示する。</t>
+  </si>
+  <si>
+    <t>デバフアイコン列</t>
+  </si>
+  <si>
+    <t>HPオーブ付近(画面下端から140px上、X=160起点)に28x28pxのアイコンを6px間隔で横に並べる。Ignite/Bleed/Poison/Chill/Freeze/Shock/Stunの発生中のもののみ3文字略称(IGN/BLD/PSN/CHL/FRZ/SHK/STN)と残り時間を表示する。</t>
+  </si>
+  <si>
+    <t>ステータステキスト</t>
+  </si>
+  <si>
+    <t>画面左上(10,10)にLv/XP(現在値/次レベル必要値)/STR/DEX/INTを常時テキスト表示する。</t>
+  </si>
+  <si>
+    <t>モーダルパネル共通仕様(実装確定)</t>
+  </si>
+  <si>
+    <t>パネルサイズ・配置</t>
+  </si>
+  <si>
+    <t>キャラクターシート/インベントリ/ベンダー/スキルジェムは幅620x480px、パッシブツリーのみ幅700x650px(ツリー表示領域560px+フッター90px)で、いずれも画面中央に配置する。背景色RGBA(15,15,20,235)+アウトライン(RGB 150,150,160、太さ2px)で統一する。</t>
+  </si>
+  <si>
+    <t>排他制御とポーズ</t>
+  </si>
+  <si>
+    <t>上記いずれかのパネル、またはキーバインド設定画面を開くと他の全パネルを自動的に閉じ、同時に複数開くことはできない。いずれかが開いている間は敵AI・移動・物理演算・当たり判定・アイテム取得・ボスフェーズ等ワールドシミュレーションを一時停止し、パネル自体の操作(UI入力)のみ受け付ける。</t>
+  </si>
+  <si>
+    <t>既存のNo7(死亡時処理)等と異なりメニュー起因の一時停止として新規に明記。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Smith of Kitava(Warrior)</t>
+  </si>
+  <si>
+    <t>巨大な鎚を用いた広範囲の物理/Fire複合攻撃と、防具の重さを活かした耐久強化を軸にするAscendancy(Dawn of the Hunt追加)。</t>
+  </si>
+  <si>
+    <t>本家PoE2参考(2026-09時点)。パッチで詳細が変わる可能性がある参考情報。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Martial Artist(Monk)</t>
+  </si>
+  <si>
+    <t>武器を持たない徒手空拳の連続コンボに特化し、素早い連打とコンボ継続で火力を積み上げるAscendancy(Return of the Ancients追加)。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Lich(Witch)</t>
+  </si>
+  <si>
+    <t>自身のLifeを闇の力に変換し、Chaosダメージと自己犠牲的な強化を軸に戦うAscendancy(Dawn of the Hunt追加)。</t>
+  </si>
+  <si>
+    <t>Ascendancy詳細: Tactician(Mercenary)</t>
+  </si>
+  <si>
+    <t>設置物やサポート火力を軸に、仲間(または自身のミニオン/装置)との連携で戦線を維持するAscendancy(Dawn of the Hunt追加)。</t>
+  </si>
+  <si>
+    <t>Huntressクラス(参考)</t>
+  </si>
+  <si>
+    <t>Spear(片手武器、Str/Dex要求)とBuckler(小型盾)を主軸とし、近接と投擲(遠距離)を1本の武器でシームレスに使い分けるハイブリッド近接クラス。Ascendancyは Ritualist/Amazon/Spirit Walker の3種。</t>
+  </si>
+  <si>
+    <t>本家PoE2で"Dawn of the Hunt"(2025年4月)にて追加された7クラス目。クラス項目(No9)の訂正内容を補足。</t>
+  </si>
+  <si>
+    <t>PvP方針</t>
+  </si>
+  <si>
+    <t>本家PoE2同様、PvP(対人戦)はコアコンテンツと位置付けず、PvE(対モンスター戦)中心の設計を基本方針とする。専用アリーナ等の対人コンテンツは現時点の本仕様の対象外とし、将来的な検討事項とする。</t>
+  </si>
+  <si>
+    <t>既存版・追加版ともにPvPへの言及が無かったため、方針として明記。</t>
+  </si>
+  <si>
+    <t>コントローラー操作(参考)</t>
+  </si>
+  <si>
+    <t>スティック/ボタン割当の基本方針</t>
+  </si>
+  <si>
+    <t>左スティック=移動、右スティック=照準(オートターゲット併用可能)、L1/R1等のショルダーボタンにスキルスロット、L2/R2にRoll等の主要アクションを割り当てる。詳細なボタンマップは本家PoE2のController UIを参考に別途策定する。</t>
+  </si>
+  <si>
+    <t>既存のController UI項目(No328)の補足。現行のC++/SFML実装はキーボード/マウス専用でコントローラー入力は未実装。</t>
+  </si>
+  <si>
+    <t>実装状況</t>
+  </si>
+  <si>
+    <t>実装状況(2026-09時点)</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装は、本カテゴリが定義するUncut Skill/Support Gem・Gem経験値/Lv・Quality・Spiritリソースを持たない。実際にはSkillGemData(固定の名前付き8種)を5スロットへ無コストかつ何度でも自由に付け替えるだけの簡易システムである。</t>
+  </si>
+  <si>
+    <t>仕様書と実装の乖離を明記。今後の実装拡張時の差分把握用。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装は、本カテゴリが定義するAscendancy・Ascendancy専用パッシブツリー・Trial of the Sekhemas等のルーグライク試練を持たない。実際には全クラス共通の単一パッシブツリー(PassiveTreeData)のみ実装済みで、Ascendancy自体が存在しない。</t>
+  </si>
+  <si>
+    <t>仕様書と実装の乖離を明記。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装は、本カテゴリが定義する武器セットA/B切替・Charm・Jewelを持たない。実際には9スロット固定装備+Prefix/Suffix affix+レアリティ4段階(EquipmentSystem)のみ実装済みである。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装は完全ローカル・シングルプレイヤーであり、本カテゴリが定義するパーティ/協力プレイ/ドロップ共有等のマルチプレイ機能は一切実装されていない。本カテゴリは将来のオンライン化を見据えた本家PoE2準拠の設計方針として記載している。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装はアカウント認証・サーバーインスタンス・チャット等を一切持たないスタンドアロン実行ファイルである。本カテゴリの内容は将来オンライン化する場合の設計方針として記載している。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装はCampaignManager::SaveToDisk/LoadFromDiskによるローカルファイル保存のみを行う。本カテゴリが定義するサーバー側永続化・League別分離管理・Cross-Save等は未実装である。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装は課金・アカウント基盤・MTX・Stashタブ購入等を一切持たない。本カテゴリは将来商用展開する場合の設計方針として記載している。</t>
+  </si>
+  <si>
+    <t>状態異常耐性Charm例</t>
+  </si>
+  <si>
+    <t>一定時間、Freeze/Chill/Shock等の特定状態異常を無効化するCharm。Flaskと同様にCharge制で使用回数を得る。</t>
+  </si>
+  <si>
+    <t>本家PoE2のCharm枠(既存のNo110)を参考にした具体例。</t>
+  </si>
+  <si>
+    <t>即時回復Charm例</t>
+  </si>
+  <si>
+    <t>使用時にLifeを瞬時に一定量回復するCharm。Flaskと役割は近いが専用スロットを消費し、Flaskとは独立してCharge/使用回数を管理する。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装(ItemFactory.h)は、本カテゴリが定義するTier/Weight/Mod Pool/Local・Global区分/タグ/Mod競合/Implicit Modを持たない簡易システムである。Prefix/Suffixそれぞれ固定4種・9種の候補から等確率抽選するのみで、Item Levelによる上位Tier解放もなく、affix.valueをItem Level x 乱数(0.85〜1.15倍)で連続的にスケーリングするだけである。Magicアイテムは本家仕様(Prefix1+Suffix1の計2個まで付与可能)と異なり、Prefix/Suffixいずれか1個のみが付与される簡易実装。Rareアイテムは本家同様Prefix最大3+Suffix最大3(計6)まで独立抽選する。ItemRarity::Uniqueという列挙値は存在するがRollRarity()の抽選対象外のため、現状ドロップ・クラフトのいずれでもUniqueアイテムは生成されない(Unique固有効果システムも未実装)。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装(CurrencySystem.h)はOrb of Transmutation/Regal/Chaos/Alchemy/Augmentation/Annulment/Chance/Scouringの8種のみを実装し、本家に存在するExalted Orb・Divine Orb、およびVaal Orbによる不可逆Corruptionは未実装である。各CurrencyはUI操作を介さず、装備中のアイテムに直接触れる(ApplyCurrency呼び出し)と即座に効果が適用される設計で、本家のようにインベントリ内の未装備アイテムへドラッグ操作で使用するUIフローは無い。Chaos Orbは本家の代表的な効果である「Rare装備のMod全体を再抽選する」挙動として実装済み。Quality変更・Socket/Rune処理・Crafting Bench的な確定クラフト機能・クラフト補助アイテム(Omen的要素)はいずれも未実装である。</t>
   </si>
 </sst>
 </file>
@@ -3730,7 +3736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21598642-ADD6-49AB-8A70-AACAEBDDCD67}">
-  <dimension ref="A1:F460"/>
+  <dimension ref="A1:F462"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -3894,7 +3900,7 @@
       </c>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -3912,7 +3918,7 @@
       </c>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4280,7 +4286,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="75" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -4744,7 +4750,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -10610,7 +10616,7 @@
       </c>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A412" s="2">
         <v>411</v>
       </c>
@@ -10630,7 +10636,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="413" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
       <c r="A413" s="2">
         <v>412</v>
       </c>
@@ -10670,7 +10676,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="415" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A415" s="2">
         <v>414</v>
       </c>
@@ -10690,7 +10696,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="416" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A416" s="2">
         <v>415</v>
       </c>
@@ -10930,7 +10936,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="428" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A428" s="2">
         <v>427</v>
       </c>
@@ -10986,7 +10992,7 @@
       </c>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A431" s="2">
         <v>430</v>
       </c>
@@ -11040,7 +11046,7 @@
       </c>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A434" s="2">
         <v>433</v>
       </c>
@@ -11060,7 +11066,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="435" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
       <c r="A435" s="2">
         <v>434</v>
       </c>
@@ -11078,7 +11084,7 @@
       </c>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A436" s="2">
         <v>435</v>
       </c>
@@ -11098,7 +11104,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="437" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A437" s="2">
         <v>436</v>
       </c>
@@ -11116,7 +11122,7 @@
       </c>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A438" s="2">
         <v>437</v>
       </c>
@@ -11134,7 +11140,7 @@
       </c>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A439" s="2">
         <v>438</v>
       </c>
@@ -11154,7 +11160,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="440" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A440" s="2">
         <v>439</v>
       </c>
@@ -11172,7 +11178,7 @@
       </c>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A441" s="2">
         <v>440</v>
       </c>
@@ -11190,7 +11196,7 @@
       </c>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A442" s="2">
         <v>441</v>
       </c>
@@ -11226,7 +11232,7 @@
       </c>
       <c r="F443" s="3"/>
     </row>
-    <row r="444" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A444" s="2">
         <v>443</v>
       </c>
@@ -11244,7 +11250,7 @@
       </c>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A445" s="2">
         <v>444</v>
       </c>
@@ -11264,7 +11270,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="447" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A447" s="2">
         <v>446</v>
       </c>
@@ -11284,7 +11290,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A448" s="2">
         <v>447</v>
       </c>
@@ -11304,7 +11310,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="449" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A449" s="2">
         <v>448</v>
       </c>
@@ -11324,7 +11330,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="450" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A450" s="2">
         <v>449</v>
       </c>
@@ -11344,7 +11350,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="451" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A451" s="2">
         <v>450</v>
       </c>
@@ -11364,7 +11370,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="452" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A452" s="2">
         <v>451</v>
       </c>
@@ -11384,7 +11390,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="453" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A453" s="2">
         <v>452</v>
       </c>
@@ -11404,7 +11410,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="454" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A454" s="2">
         <v>453</v>
       </c>
@@ -11424,7 +11430,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="455" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A455" s="2">
         <v>454</v>
       </c>
@@ -11444,7 +11450,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="456" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A456" s="2">
         <v>455</v>
       </c>
@@ -11464,7 +11470,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="457" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:6" ht="75" x14ac:dyDescent="0.4">
       <c r="A457" s="2">
         <v>456</v>
       </c>
@@ -11484,7 +11490,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A458" s="2">
         <v>457</v>
       </c>
@@ -11504,7 +11510,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="459" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A459" s="2">
         <v>458</v>
       </c>
@@ -11542,6 +11548,34 @@
       </c>
       <c r="F460" s="3" t="s">
         <v>1077</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A461">
+        <v>460</v>
+      </c>
+      <c r="B461" t="s">
+        <v>293</v>
+      </c>
+      <c r="D461" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E461" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A462">
+        <v>461</v>
+      </c>
+      <c r="B462" t="s">
+        <v>322</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E462" t="s">
+        <v>1089</v>
       </c>
     </row>
   </sheetData>
@@ -11960,7 +11994,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -11994,7 +12028,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>27</v>
       </c>

--- a/PoE2_仕様書.xlsx
+++ b/PoE2_仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazus\source\repos\企業用\POE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B659B398-4E4E-498D-9C68-CD17AC21923A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1532CE02-601C-4D20-BBAB-E9E4652F7D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91AE84DB-8705-4A0B-863F-59311E04910A}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="1092">
   <si>
     <t>No</t>
   </si>
@@ -3314,6 +3314,12 @@
   </si>
   <si>
     <t>現在のC++/SFML実装(CurrencySystem.h)はOrb of Transmutation/Regal/Chaos/Alchemy/Augmentation/Annulment/Chance/Scouringの8種のみを実装し、本家に存在するExalted Orb・Divine Orb、およびVaal Orbによる不可逆Corruptionは未実装である。各CurrencyはUI操作を介さず、装備中のアイテムに直接触れる(ApplyCurrency呼び出し)と即座に効果が適用される設計で、本家のようにインベントリ内の未装備アイテムへドラッグ操作で使用するUIフローは無い。Chaos Orbは本家の代表的な効果である「Rare装備のMod全体を再抽選する」挙動として実装済み。Quality変更・Socket/Rune処理・Crafting Bench的な確定クラフト機能・クラフト補助アイテム(Omen的要素)はいずれも未実装である。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装(CharacterStats.h/CombatMath.h/EquipmentSystem.h)は、本カテゴリのResistances/Block/各種上限値を以下のように簡略化して実装している。Resistancesは仕様通りFire/Cold/Lightning/Chaosの4種・上限75%だが、加えて本家のCruel(高難易度)再攻略時の耐性ペナルティに相当する仕様として、幕(Act)を1つクリアするごとに非Chaos耐性3種へ-10%の永続ペナルティを課す(CampaignManager::CompleteCurrentZoneAndAdvance、全6幕クリアで-60%)。Blockは本家がShield/Staff等の特定装備でのみ発生し攻撃用/呪文用を別々に持てるのに対し、実装は盾スロット自体が存在しないため、AffixStat::BlockChanceという汎用サフィックス(CritChance/MoveSpeed等と同枠)としてどの装備にも付与されうる単一の値のみを持つ(攻撃/呪文の区別なし、CombatMath::ApplyDamageで命中判定後にロールしヒットを丸ごと無効化、上限75%)。Spell Suppressionは本実装に攻撃/呪文の区別自体が無いため未実装。</t>
+  </si>
+  <si>
+    <t>現在のC++/SFML実装(CampaignManager.cpp)のAct構成は、本カテゴリが定義する「Act1〜3(Normal)+同エリアをCruel難易度で再攻略」という設計ではなく、Act1/Act2/幕間I/Act3/Act4/幕間IIという6つの互いに異なるエリア(固有の敵タイプ・ボス・マップサイズを持つ)を1本道で順に進む構成である(BuildActs)。ただし本家のCruel移行時の耐性ペナルティに相当する仕組みとしては、この6エリアそれぞれのクリア時に耐性-10%(計-60%)を課すことで、本家の「全6章相当クリアで-60%」という数値上の帳尻を合わせている(02_プレイヤーキャラクター仕様の実装状況を参照)。</t>
   </si>
 </sst>
 </file>
@@ -3736,7 +3742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21598642-ADD6-49AB-8A70-AACAEBDDCD67}">
-  <dimension ref="A1:F462"/>
+  <dimension ref="A1:F464"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -11576,6 +11582,40 @@
       </c>
       <c r="E462" t="s">
         <v>1089</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A463">
+        <v>462</v>
+      </c>
+      <c r="B463" t="s">
+        <v>26</v>
+      </c>
+      <c r="D463" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E463" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F463" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A464">
+        <v>463</v>
+      </c>
+      <c r="B464" t="s">
+        <v>456</v>
+      </c>
+      <c r="D464" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E464" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F464" t="s">
+        <v>1077</v>
       </c>
     </row>
   </sheetData>

--- a/PoE2_仕様書.xlsx
+++ b/PoE2_仕様書.xlsx
@@ -8,13 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazus\source\repos\企業用\POE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1532CE02-601C-4D20-BBAB-E9E4652F7D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DB8EAA-A9E2-4660-A319-D810A8E8B590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{91AE84DB-8705-4A0B-863F-59311E04910A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="15" xr2:uid="{91AE84DB-8705-4A0B-863F-59311E04910A}"/>
   </bookViews>
   <sheets>
     <sheet name="PoE2_仕様一覧" sheetId="1" r:id="rId1"/>
     <sheet name="サンプル例参考" sheetId="2" r:id="rId2"/>
+    <sheet name="ジェムシステム仕様_ベース" sheetId="3" r:id="rId3"/>
+    <sheet name="SkillGem仕様" sheetId="4" r:id="rId4"/>
+    <sheet name="SupportGem仕様" sheetId="5" r:id="rId5"/>
+    <sheet name="SpiritGem_Persistent仕様" sheetId="6" r:id="rId6"/>
+    <sheet name="Spiritリソース仕様" sheetId="7" r:id="rId7"/>
+    <sheet name="UncutGem仕様" sheetId="8" r:id="rId8"/>
+    <sheet name="Gemcutting仕様" sheetId="9" r:id="rId9"/>
+    <sheet name="SkillsPanel仕様" sheetId="10" r:id="rId10"/>
+    <sheet name="SkillBar_KeyBind仕様" sheetId="11" r:id="rId11"/>
+    <sheet name="SkillActivation仕様" sheetId="12" r:id="rId12"/>
+    <sheet name="SaveLoad仕様" sheetId="13" r:id="rId13"/>
+    <sheet name="画面仕様_ジェム関連" sheetId="14" r:id="rId14"/>
+    <sheet name="キー仕様_ジェム関連" sheetId="15" r:id="rId15"/>
+    <sheet name="プロジェクト仕様_ベース" sheetId="16" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PoE2_仕様一覧!$A$1:$F$411</definedName>
@@ -44,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="1416">
   <si>
     <t>No</t>
   </si>
@@ -3320,13 +3334,985 @@
   </si>
   <si>
     <t>現在のC++/SFML実装(CampaignManager.cpp)のAct構成は、本カテゴリが定義する「Act1〜3(Normal)+同エリアをCruel難易度で再攻略」という設計ではなく、Act1/Act2/幕間I/Act3/Act4/幕間IIという6つの互いに異なるエリア(固有の敵タイプ・ボス・マップサイズを持つ)を1本道で順に進む構成である(BuildActs)。ただし本家のCruel移行時の耐性ペナルティに相当する仕組みとしては、この6エリアそれぞれのクリア時に耐性-10%(計-60%)を課すことで、本家の「全6章相当クリアで-60%」という数値上の帳尻を合わせている(02_プレイヤーキャラクター仕様の実装状況を参照)。</t>
+  </si>
+  <si>
+    <t>ジェムシステム</t>
+  </si>
+  <si>
+    <t>Skill Gemの定義・役割</t>
+  </si>
+  <si>
+    <t>Skill Gem Level(レベルアップ方法・既存Skillの強化)</t>
+  </si>
+  <si>
+    <t>Skill Gem InstanceとSkill Instance(Runtime)の分離</t>
+  </si>
+  <si>
+    <t>Support Gemの定義・役割</t>
+  </si>
+  <si>
+    <t>Support Socket(初期数・拡張方法・上限)</t>
+  </si>
+  <si>
+    <t>Support Compatibility判定(対応/非対応の条件)</t>
+  </si>
+  <si>
+    <t>Support Category(同一Skill内の重複制限)</t>
+  </si>
+  <si>
+    <t>Spirit Gem / Persistent Skill</t>
+  </si>
+  <si>
+    <t>Spirit Gemの定義・役割</t>
+  </si>
+  <si>
+    <t>Persistent Skillの状態(Inactive/Active等)</t>
+  </si>
+  <si>
+    <t>Permanent Minion仕様(スポーン・死亡・リスポーン)</t>
+  </si>
+  <si>
+    <t>Trigger/Meta Persistent Skill仕様</t>
+  </si>
+  <si>
+    <t>Spirit(リソース)</t>
+  </si>
+  <si>
+    <t>Max/Reserved/Available Spiritの計算式</t>
+  </si>
+  <si>
+    <t>Spirit取得元(装備/パッシブ/その他)</t>
+  </si>
+  <si>
+    <t>Reservation超過時の挙動</t>
+  </si>
+  <si>
+    <t>Uncut Gem</t>
+  </si>
+  <si>
+    <t>Uncut Gemの種類(Skill/Support/Spirit)</t>
+  </si>
+  <si>
+    <t>ドロップ仕様(Area Level・Drop Level連動)</t>
+  </si>
+  <si>
+    <t>Pickup仕様</t>
+  </si>
+  <si>
+    <t>Inventory格納仕様(容量・満杯時挙動)</t>
+  </si>
+  <si>
+    <t>Gemcutting</t>
+  </si>
+  <si>
+    <t>Gemcutting画面の表示項目</t>
+  </si>
+  <si>
+    <t>Engrave(確定)フロー・消費タイミング</t>
+  </si>
+  <si>
+    <t>既存Skillのレベルアップ経路</t>
+  </si>
+  <si>
+    <t>Skills Panel</t>
+  </si>
+  <si>
+    <t>表示項目(Lv/Mana/Spirit/Support/有効無効理由等)</t>
+  </si>
+  <si>
+    <t>Support装着操作(クリック/ドラッグ&amp;ドロップ)</t>
+  </si>
+  <si>
+    <t>Skill Bar / Key Binding</t>
+  </si>
+  <si>
+    <t>Skill BarとSkills Panelの役割分担</t>
+  </si>
+  <si>
+    <t>キーバインド表示仕様(実キー反映)</t>
+  </si>
+  <si>
+    <t>Skill Activation</t>
+  </si>
+  <si>
+    <t>CanUseSkill判定項目の一覧</t>
+  </si>
+  <si>
+    <t>Cooldown/Mana/Weapon要件の扱い</t>
+  </si>
+  <si>
+    <t>Save/Load</t>
+  </si>
+  <si>
+    <t>保存対象データ一覧</t>
+  </si>
+  <si>
+    <t>Load時の復元順序</t>
+  </si>
+  <si>
+    <t>詳細シート</t>
+  </si>
+  <si>
+    <t>SkillGem仕様</t>
+  </si>
+  <si>
+    <t>SupportGem仕様</t>
+  </si>
+  <si>
+    <t>SpiritGem_Persistent仕様</t>
+  </si>
+  <si>
+    <t>Spiritリソース仕様</t>
+  </si>
+  <si>
+    <t>UncutGem仕様</t>
+  </si>
+  <si>
+    <t>Gemcutting仕様</t>
+  </si>
+  <si>
+    <t>SkillsPanel仕様</t>
+  </si>
+  <si>
+    <t>SkillBar_KeyBind仕様</t>
+  </si>
+  <si>
+    <t>SkillActivation仕様</t>
+  </si>
+  <si>
+    <t>SaveLoad仕様</t>
+  </si>
+  <si>
+    <t>画面仕様</t>
+  </si>
+  <si>
+    <t>Skills Panel: 画面構成(スロット配置・パネルサイズ・座標)</t>
+  </si>
+  <si>
+    <t>Skills Panel: スキルスロット表示内容(アイコン/Lv/Mana/Cooldown等)</t>
+  </si>
+  <si>
+    <t>Skills Panel: Supportソケット表示(空き/装着済み/要件未達の見た目)</t>
+  </si>
+  <si>
+    <t>Skills Panel: Spiritスロット表示(ON/OFF状態・予約量)</t>
+  </si>
+  <si>
+    <t>Skills Panel: 無効化理由の表示方法(グレーアウト+理由テキスト)</t>
+  </si>
+  <si>
+    <t>Skills Panel: 開閉方法・他パネルとの排他/同時表示関係</t>
+  </si>
+  <si>
+    <t>Gem Cutting画面: 画面構成・レイアウト</t>
+  </si>
+  <si>
+    <t>Gem Cutting画面: 候補一覧の表示項目(名前/アイコン/カテゴリ/タグ/要求武器/要求Lv/Gem Lv/Tier/Mana Cost/説明)</t>
+  </si>
+  <si>
+    <t>Gem Cutting画面: 選択・確定(Engrave)操作</t>
+  </si>
+  <si>
+    <t>Gem Cutting画面: キャンセル操作</t>
+  </si>
+  <si>
+    <t>Inventory画面: Uncut Gemの表示(アイコン/レベル/種別)</t>
+  </si>
+  <si>
+    <t>Inventory画面: Uncut Gem使用操作の起点(右クリック等)</t>
+  </si>
+  <si>
+    <t>Inventory画面: 満杯時の表示</t>
+  </si>
+  <si>
+    <t>Tooltip: Skill Gemの表示項目</t>
+  </si>
+  <si>
+    <t>Tooltip: Support Gemの表示項目</t>
+  </si>
+  <si>
+    <t>Tooltip: Spirit Gemの表示項目</t>
+  </si>
+  <si>
+    <t>Tooltip: 使用不可理由の表示(共通仕様)</t>
+  </si>
+  <si>
+    <t>キー仕様</t>
+  </si>
+  <si>
+    <t>パネル開閉: OpenSkills(Skills Panelを開く)</t>
+  </si>
+  <si>
+    <t>パネル開閉: OpenInventory(インベントリを開く)</t>
+  </si>
+  <si>
+    <t>パネル開閉: 閉じる操作(Esc等・パネルごとの優先順位)</t>
+  </si>
+  <si>
+    <t>ゲーム内操作: SkillSlot1〜5(スキル使用キー)</t>
+  </si>
+  <si>
+    <t>ゲーム内操作: Interact/Pickup(拾得)</t>
+  </si>
+  <si>
+    <t>ゲーム内操作: UseItem/ContextAction(Uncut Gem使用)</t>
+  </si>
+  <si>
+    <t>ゲーム内操作: Dodge(回避)</t>
+  </si>
+  <si>
+    <t>UI内操作: UISelect(確定)</t>
+  </si>
+  <si>
+    <t>UI内操作: UIBack(戻る/キャンセル)</t>
+  </si>
+  <si>
+    <t>UI内操作: UIContextAction(右クリック相当の操作)</t>
+  </si>
+  <si>
+    <t>リバインド仕様: リバインド可能な操作の一覧</t>
+  </si>
+  <si>
+    <t>リバインド仕様: リバインド不可(UI固定操作)の一覧</t>
+  </si>
+  <si>
+    <t>リバインド仕様: UI表示への反映方法(実キー表示、例[G] Skills)</t>
+  </si>
+  <si>
+    <t>画面仕様_ジェム関連</t>
+  </si>
+  <si>
+    <t>キー仕様_ジェム関連</t>
+  </si>
+  <si>
+    <t>エンドゲーム/マップ</t>
+  </si>
+  <si>
+    <t>Waystoneのティア仕様(1〜15)</t>
+  </si>
+  <si>
+    <t>Waystoneの入手方法(ドロップ確率・ティア決定ロジック)</t>
+  </si>
+  <si>
+    <t>Waystoneの消費(マップ開放操作)</t>
+  </si>
+  <si>
+    <t>所持数の扱い(最高ティア自動消費 等)</t>
+  </si>
+  <si>
+    <t>エンドゲームマップ</t>
+  </si>
+  <si>
+    <t>マップ生成仕様(Tierによる差分)</t>
+  </si>
+  <si>
+    <t>Tierによる耐性スケーリング仕様</t>
+  </si>
+  <si>
+    <t>マップクリア条件(ボス/Rare討伐等)</t>
+  </si>
+  <si>
+    <t>マップ内モンスター構成</t>
+  </si>
+  <si>
+    <t>Act進行</t>
+  </si>
+  <si>
+    <t>Act構成(Act1-4/幕間/Endgame)</t>
+  </si>
+  <si>
+    <t>ゾーン遷移仕様(タウン⇔戦闘)</t>
+  </si>
+  <si>
+    <t>幕クリア時の耐性ペナルティ仕様</t>
+  </si>
+  <si>
+    <t>戦闘計算</t>
+  </si>
+  <si>
+    <t>命中率計算式</t>
+  </si>
+  <si>
+    <t>Armour軽減計算式</t>
+  </si>
+  <si>
+    <t>属性耐性(上限・計算式)</t>
+  </si>
+  <si>
+    <t>エナジーシールドの優先順位</t>
+  </si>
+  <si>
+    <t>ブロック判定仕様</t>
+  </si>
+  <si>
+    <t>クリティカル計算式</t>
+  </si>
+  <si>
+    <t>Leech</t>
+  </si>
+  <si>
+    <t>Leech率・上限仕様</t>
+  </si>
+  <si>
+    <t>状態異常</t>
+  </si>
+  <si>
+    <t>Ignite仕様(発生条件・DPS・持続時間)</t>
+  </si>
+  <si>
+    <t>Chill/Freeze仕様</t>
+  </si>
+  <si>
+    <t>Shock仕様</t>
+  </si>
+  <si>
+    <t>Poison仕様</t>
+  </si>
+  <si>
+    <t>Bleed仕様</t>
+  </si>
+  <si>
+    <t>Stun仕様</t>
+  </si>
+  <si>
+    <t>装備・アイテム</t>
+  </si>
+  <si>
+    <t>スロット構成(9スロット)</t>
+  </si>
+  <si>
+    <t>PowerScore計算・比較仕様</t>
+  </si>
+  <si>
+    <t>Affix(Mod)</t>
+  </si>
+  <si>
+    <t>Prefix/Suffixプール一覧</t>
+  </si>
+  <si>
+    <t>Affixのロール仕様(Tier・値幅)</t>
+  </si>
+  <si>
+    <t>アイテム生成</t>
+  </si>
+  <si>
+    <t>レアリティ抽選仕様</t>
+  </si>
+  <si>
+    <t>Item Level基準のスケーリング</t>
+  </si>
+  <si>
+    <t>売却額計算式</t>
+  </si>
+  <si>
+    <t>拾得・インベントリ</t>
+  </si>
+  <si>
+    <t>インベントリ格納仕様(グリッドサイズ)</t>
+  </si>
+  <si>
+    <t>満杯時の挙動(自動売却等)</t>
+  </si>
+  <si>
+    <t>ドラッグ&amp;ドロップ/売却/破棄操作</t>
+  </si>
+  <si>
+    <t>通貨・クラフト</t>
+  </si>
+  <si>
+    <t>Currency種別</t>
+  </si>
+  <si>
+    <t>Currency一覧と効果(Transmutation/Augmentation/Alchemy/Regal/Chaos/Annulment/Scouring/Chance/Jeweller's Orb/Regret Orb等)</t>
+  </si>
+  <si>
+    <t>購入/売却/Buyback仕様</t>
+  </si>
+  <si>
+    <t>在庫リロール仕様(価格・頻度)</t>
+  </si>
+  <si>
+    <t>キャラクター進行</t>
+  </si>
+  <si>
+    <t>XP/レベリング</t>
+  </si>
+  <si>
+    <t>経験値計算式</t>
+  </si>
+  <si>
+    <t>レベルアップ処理・上限</t>
+  </si>
+  <si>
+    <t>パッシブツリー</t>
+  </si>
+  <si>
+    <t>ツリー構造(ノード数・分岐)</t>
+  </si>
+  <si>
+    <t>割り振り仕様(隣接条件)</t>
+  </si>
+  <si>
+    <t>解放(Respec)仕様(Regret Orb)</t>
+  </si>
+  <si>
+    <t>モンスター/敵AI</t>
+  </si>
+  <si>
+    <t>アーキタイプ</t>
+  </si>
+  <si>
+    <t>近接(通常追跡)</t>
+  </si>
+  <si>
+    <t>遠距離(kite/射撃)</t>
+  </si>
+  <si>
+    <t>範囲攻撃</t>
+  </si>
+  <si>
+    <t>召喚</t>
+  </si>
+  <si>
+    <t>突進(テレグラフ→突進→クールダウン)</t>
+  </si>
+  <si>
+    <t>ボス</t>
+  </si>
+  <si>
+    <t>ボスフェーズ(HP閾値でEnrage等)</t>
+  </si>
+  <si>
+    <t>UI(ゲーム全体)</t>
+  </si>
+  <si>
+    <t>キャラクターシート</t>
+  </si>
+  <si>
+    <t>表示項目一覧</t>
+  </si>
+  <si>
+    <t>インベントリUI</t>
+  </si>
+  <si>
+    <t>パネル構成・操作仕様</t>
+  </si>
+  <si>
+    <t>入力/キーバインド(全体)</t>
+  </si>
+  <si>
+    <t>リバインド可能操作</t>
+  </si>
+  <si>
+    <t>一覧(移動/ロール/スキル5枠/UIパネル開閉/Vendorリロール等)</t>
+  </si>
+  <si>
+    <t>固定UI操作</t>
+  </si>
+  <si>
+    <t>一覧(カーソル移動/確定/戻る/売却等)</t>
+  </si>
+  <si>
+    <t>セーブ/ロード(全体)</t>
+  </si>
+  <si>
+    <t>保存対象</t>
+  </si>
+  <si>
+    <t>キャラクターステータス/装備/インベントリ/パッシブ/ジェム/Waystone/進行状況 等</t>
+  </si>
+  <si>
+    <t>復元順序</t>
+  </si>
+  <si>
+    <t>Load時の復元順序仕様</t>
+  </si>
+  <si>
+    <t>デバッグツール</t>
+  </si>
+  <si>
+    <t>既存デバッグ機能</t>
+  </si>
+  <si>
+    <t>シーン管理/カメラ/パフォーマンス/ジェムデバッグ等の一覧</t>
+  </si>
+  <si>
+    <t>プレイヤーが実際に使用するActive Skillを提供するジェム。SkillGemData::GemDefinitionが静的カタログ(id/SkillData/GemAttribute/baseRequirement)を保持し、所持済みの個体はOwnedGemInstance(SkillGemInventoryComponent.ownedGems、isSupport=false)として管理する。装着時はSkillGemScaling::BuildEquippedSkillDataでカタログ+レベル+装着中Supportから毎回ライブなSkillDataを組み立て直す。</t>
+  </si>
+  <si>
+    <t>Support Gem/Spirit Gemとは明確に別カテゴリ(behaviorType==Auraまたは==MinionをSkillGemData::IsSpiritBehaviorで判定しSpirit枠専用に振り分ける)。</t>
+  </si>
+  <si>
+    <t>Gemは1〜20のLvを持ち(OwnedGemInstance::level)、SkillGemScaling::ScaledDamage/ScaledMpCost/RequiredStatが(1+(level-1)*係数)の線形スケーリングでダメージ・マナ消費・装備要件を算出する。レベルアップは敵撃破のExpではなく、より高LvのUncut Skill Gemを同じGemIdでGem Cuttingにかけることで実現する(GemIdentifySystem::Identifyが既存Instanceを検出しレベルのみ引き上げ)。</t>
+  </si>
+  <si>
+    <t>PoE2本家の「装着スキルがキャラExpの一部を共有してLvが自動上昇する」仕様とは異なり、本実装はキル経験値によるGem自動成長を採用していない(仕様書§27の指示にも合致する簡略化)。</t>
+  </si>
+  <si>
+    <t>所有データであるOwnedGemInstance(Lv/ソケット数/装着中Support等)と、実行時データであるPlayerSkill.skills[i](SkillData、cooldown/currentCooldown等の可変状態を含む)は明確に分離されている。SkillGemScaling::BuildEquippedSkillDataが前者から後者を都度再構築する一方向のデータフローで、Runtime側の値を直接Ownedデータへ書き戻すことはない。</t>
+  </si>
+  <si>
+    <t>単独では使用できず、装着先Skillのダメージ/クールダウン/マナ消費/範囲/持続時間へ乗算補正を適用する拡張ジェム。SupportGemData::SupportGemDefinitionが8種の静的カタログを持ち(Added Damage/Brutality/Faster Attacks/Efficiency/Increased Area/Increased Duration/Concentrated Effect/Elemental Focus)、適用はSupportGemSystem::Applyが担う。</t>
+  </si>
+  <si>
+    <t>PoE2本家のような加算/上書き等の複雑なMod体系ではなく、乗算のみで完結させて実装を単純化している。</t>
+  </si>
+  <si>
+    <t>Skill/Spirit Gem個体(OwnedGemInstance)はmaxSockets(初期2、上限5)個のSupportソケットを持つ。拡張はCurrencyType::JewellersOrb(CharacterStatsComponent::jewellersOrbsに蓄積)をSkillGemSystem画面のボタンで1個消費して+1する。</t>
+  </si>
+  <si>
+    <t>本家のLesser/Greater/Perfect Jeweller Orb(3/4/5ソケットへ直接セット)を簡略化し、単一種で+1ずつ拡張する方式にしている。</t>
+  </si>
+  <si>
+    <t>SkillTags::TagsFor(behaviorType, element)がSkillのタグ(Attack/Spell/Melee/Projectile/AreaEffect/Duration/Movement/Physical/Elemental/Chaos)を機械的に導出し、SupportGemDefinition::requiredTag(単一タグ、Noneなら無条件)との適合をSkillTags::IsCompatibleが判定する。SkillGemSystem::SupportOptionsが適合するSupportのみをピッカーへ表示する。</t>
+  </si>
+  <si>
+    <t>構造化されたReasonCode/ReasonText形式ではなく、判定はbool一つのみ(不適合時のメッセージは呼び出し側の固定文字列)。</t>
+  </si>
+  <si>
+    <t>SupportGemDefinition::category(SupportCategory: DamageMult/Speed/Utility/AreaMod/Duration)を持ち、同一スキルの別ソケットへ同じCategoryのSupportを重複装着することをSkillGemSystem::AssignSupport/HasCategoryConflictが禁止する。同じCategoryを別スキルへ装着するのは制限しない(キャラクター全体の制限ではない)。</t>
+  </si>
+  <si>
+    <t>2026-09-17時点の追加仕様(実バグ修正の一環として新設)。</t>
+  </si>
+  <si>
+    <t>Spiritを予約して常時効果を維持するジェムのカテゴリ。behaviorTypeがAura(ステータス加算バフ、SkillData::auraEffectを装備ベースへ直接Apply/RemoveAffix)またはMinion(永続召喚、後述)のどちらかで、SkillGemData::IsSpiritBehaviorで共通のSpirit枠カテゴリとして扱われる。</t>
+  </si>
+  <si>
+    <t>SpiritGemLoadoutComponent.active[5]によるON/OFFの2値のみで管理する(Inactive/Activating/Active/Deactivating/Disabledの5状態機械は採用していない)。ON/OFF切替はSpiritAuraSystem::TryToggleActiveが担う。</t>
+  </si>
+  <si>
+    <t>発動に時間のかかる詠唱・演出が現状無いため2値で十分と判断した簡略化。Minion/Trigger拡張時にActivating/Deactivating相当が必要になれば拡張余地はある。</t>
+  </si>
+  <si>
+    <t>SkillBehaviorType::MinionをONにするとSpiritAuraSystem::SetActiveがEntitySpawner::CreateMinionで召喚体を生成する(AllyTagComponent+PermanentMinionComponent)。MinionSystemが追従/近接AI・敵との接触ダメージ交換を毎フレーム処理し、死亡時はSkillをActiveのままSpiritも解放せず、SpiritGemLoadoutComponent.minionRespawnTimer(8秒固定)経過後に再スポーンする。OFFにした時だけEntity破棄+Spirit解放。サンプルジェムとしてSummon Skeleton(id16)を実装済み。</t>
+  </si>
+  <si>
+    <t>2026-09-17新規実装。本プロジェクトのCollisionSystemは元々「PlayerInputComponentを持つか否か」でしか敵味方を区別しない設計だったため、AllyTagComponentをプレイヤー自身の弾/敵接触ダメージ双方の判定から除外する最小限の変更を追加している。</t>
+  </si>
+  <si>
+    <t>未実装。</t>
+  </si>
+  <si>
+    <t>SkillDataがテーブル駆動の構造になっているため、将来ContainedSkills/TriggerCondition等のフィールドを追加する形で拡張は可能(拡張不能な設計にはなっていない)。</t>
+  </si>
+  <si>
+    <t>CharacterStatsComponent::maxSpirit(上限)とcurrentSpirit(予約済み量、Consumeではない)を持つ。Availableは表示上maxSpirit-currentSpiritとして算出され、currentSpiritはSpiritAuraSystem::SumActiveReservationsがONのSpirit Gem全部のspiritCost合計として毎回再計算する(積み上げ加算ではなく都度再計算のため状態不整合が起きない)。</t>
+  </si>
+  <si>
+    <t>AffixStat::FlatSpiritを新設し、EquipmentSystem::ApplyAffix/RemoveAffix・ItemFactory::SuffixPool経由で装備のサフィックスとしてロールされうる(他のFlat系ステータスと同じ汎用Modifierパイプライン)。開始時のBase値はEntitySpawnerで100。</t>
+  </si>
+  <si>
+    <t>2026-09-17時点でパッシブツリー側にSpirit加算ノードは未追加(装備経由のみ実装済み)。</t>
+  </si>
+  <si>
+    <t>SpiritAuraSystem::ReevaluateReservationsがGameScene::Updateから毎フレーム呼ばれ、予約合計がMaxSpiritを超えていれば末尾スロットから順にOFF化(Effect解除/Minion Despawn+Spirit解放)して自動的に予算内へ戻す。他のPersistent Skillを巻き込まない最小限のOFF化のみ行う。</t>
+  </si>
+  <si>
+    <t>「新しい構成では有効化できないことをUIへ表示する」(Activate時のNot enough Spiritメッセージ)は実装済みだが、超過時に他をOFFにする動作自体は装備を外して不足させた場合の救済として意図的に採用している(アクティブ化リクエスト時の拒否とは別のケース)。</t>
+  </si>
+  <si>
+    <t>GemPickupKind列挙(Skill/Support/Spirit)で3種を区別する。ドロップ確率はCollisionSystemで60%/20%/20%の内訳。</t>
+  </si>
+  <si>
+    <t>CollisionSystemのドロップ抽選でモンスターの強さ(maxHPから算出したitemLevel相当値)を基準にLv1〜20を3乗分布(std::pow(roll,3))でロールし、19-20が出にくいよう偏らせている。モンスターが強いほどmonsterLevelFactor分だけ底上げされる。</t>
+  </si>
+  <si>
+    <t>PoE2本家の「Area Level」という明示的なゾーン単位の値ではなく、モンスターの強さ(HP)を代理指標として使っている簡略化。</t>
+  </si>
+  <si>
+    <t>フィールド上のUncut Gemはクリックで拾得する(ItemPickupSystem::Update)。SkillGemInventoryComponent.pendingUncutGemsが上限kPendingCapacity(8)に達している場合は「Uncut gem storage full」を表示し拾得を拒否する(WorldItemは消えずその場に残る)。</t>
+  </si>
+  <si>
+    <t>Uncut Gemは装備アイテム用のInventoryComponent(グリッド)とは別の軽量キューSkillGemInventoryComponent.pendingUncutGems(vector、容量8)に格納される。使用(鑑定)されるとキューから該当indexがeraseされる。</t>
+  </si>
+  <si>
+    <t>装備アイテムと同じグリッドインベントリへ統合する設計ではなく、専用の簡易キューとして分離している(Uncut Gem専用のシンプルな保持で十分と判断)。</t>
+  </si>
+  <si>
+    <t>GemIdentifySystemが担当。ヘッダに「Uncut {種別} Gem, Level {N} - choose:」を表示し、候補一覧は各行に候補名(Skill/SpiritはGemDefinition::skill.name、SupportはSupportGemDefinition::name)のみを表示する。既存Gemの場合は「(upgrade Lv{X} -&gt; Lv{Y})」を追記する。</t>
+  </si>
+  <si>
+    <t>仕様書が求めるIcon/Category/Tags/Required Weapon/Required Level/Tier/Mana Cost/Descriptionといったリッチな表示項目は未実装(名前とアップグレード表記のみ)。</t>
+  </si>
+  <si>
+    <t>候補行をクリックすると即座にIdentifyが実行され、OwnedGemInstanceを追加(または既存インスタンスのLvを引き上げ)、pendingUncutGemsから該当indexを消費(erase)する。成功時のみ消費される(候補選択=確定のワンステップで、Preview→Engraveの2段階UIにはなっていない)。</t>
+  </si>
+  <si>
+    <t>Skill/Spirit種別の場合、Options()が既存所持Gemで「今回のUncut Gemのレベルより低いもの」のみ候補に残す。選択するとexisting-&gt;level=m_pendingLevelでレベルを直接引き上げる。Support種別はレベル概念がないため、既に所持していれば候補から除外される(アップグレードという概念自体が無い)。</t>
+  </si>
+  <si>
+    <t>SkillGemSystem(Gキー)がスキル5枠+Spirit5枠=計10枠を1画面に表示する。各スキル行は名前/Lv/Cooldown/Mana Cost/元素(該当時)+Supportソケット(空き/装着中/ソケット拡張ボタン)を表示。Spirit行は名前/Lv/Spiritコスト+ON/OFFボタンを表示する。ピッカー内では要件未達成の候補を赤字で表示する。</t>
+  </si>
+  <si>
+    <t>「無効化理由」は現状ハードコードされた固定メッセージ(例:Requires X Str)としてのみ表示され、汎用的なReasonコード経由ではない。</t>
+  </si>
+  <si>
+    <t>クリックのみで完結する(ソケットをクリック→サポート専用ピッカーが下部に表示→候補をクリックで装着)。ドラッグ&amp;ドロップは実装していない。</t>
+  </si>
+  <si>
+    <t>仕様書はドラッグ&amp;ドロップも選択肢として挙げているが、本実装のスキル系UIは全体的にクリックのみで統一する方針(AI/DECISIONS.mdの既定路線)。</t>
+  </si>
+  <si>
+    <t>本実装には両者の区別が無く、PlayerSkill.skills[0-4]に装着したSkillが同時に戦闘中の実行スロットでもある。専用のSkill Bar HUD(常時表示のスキルアイコン+クールダウン表示)は存在せず、SkillsPanel(Gキー)がconfig兼用になっている。</t>
+  </si>
+  <si>
+    <t>明確なギャップ。将来的にSkill Bar HUDを追加する場合、SkillActivation::CanUseSkillを再利用すればUIと実戦の判定を一致させられる設計にはなっている。</t>
+  </si>
+  <si>
+    <t>KeyBindings::Instance().Get(GameAction::SkillN)から取得した実キーをSkillGemSystemが[E] Fireballのように動的表示する(文字列としてハードコードしない)。既定はSkill1=E/Skill2=Q/Skill3=R/Skill4=V/Skill5=F。</t>
+  </si>
+  <si>
+    <t>SkillActivationSystem.hのSkillActivation::CanUseSkillが生存(currentHP&gt;0)/有効(isValid)/クールダウン(currentCooldown&lt;=0)/マナ(currentMP&gt;=mpCost)/武器要件(SkillTag::Attackを持つ場合は武器スロット必須)の5項目を一箇所で判定する。SkillSystem::Updateの実発動ゲートがこれを直接使用する。</t>
+  </si>
+  <si>
+    <t>Charge/Target(範囲内に敵がいるか等)は判定項目に含まれていない(本作にCharge仕様が無いため)。</t>
+  </si>
+  <si>
+    <t>発動が失敗した場合(マナ不足・クールダウン中・武器なし等)はマナ消費・クールダウン開始のいずれも発生しない(SkillSystem::UpdateはCanUseSkillがOkを返した場合のみマナ減算とActivateSkill呼び出しを行う)。</t>
+  </si>
+  <si>
+    <t>CampaignManagerがownedGems(OwnedGemInstance一覧、gemId/isSupport/level/maxSockets/support0-4)、pendingUncutGems(level/kind)、skillLoadout(5枠のgemId)、auraLoadout(5枠のgemId)、auraActive(5枠のbool)をフラットなkey=value形式でシリアライズする。</t>
+  </si>
+  <si>
+    <t>Quality/Corruption/Tierといった概念は本実装に存在しないため保存対象にも含まれない。</t>
+  </si>
+  <si>
+    <t>GameSceneコンストラクタで、ownedGemsが空でなければgemInventory.ownedGemsを復元しつつSkillGemScaling::BuildEquippedSkillDataで各スキルスロットを再構築する。pendingUncutGemsはownedGemsの有無に関わらず独立して復元する(鑑定前の初回ジェムだけ持つ状態でもロスしないため)。Spirit Loadoutはauraキーで復元するのみで、Minion Entityの再スポーンは保存対象にせずMinionSystemの毎フレームチェックに委ねる(次のtickで自動的に再生成される)。</t>
+  </si>
+  <si>
+    <t>「Definitions Load→Character Stats→Inventory→Gem Instances→Skills→Supports→Spirit Max計算→Reservations→Persistent Effects→Key Bindings」という理想的な順序とは異なり、本実装はGameScene初期化時にほぼ一括で復元する(Reservationsの整合性はReevaluateReservationsが次フレーム以降に保証する)。</t>
+  </si>
+  <si>
+    <t>SkillGemSystemは画面左上に固定パネル(kPanelX=20, kPanelY=20, kPanelW=460, kPanelH=680)を表示し、上から「Uncut Gemsチップ行」→「スキル5行」→「Spirit5行」→「候補/Supportピッカー」の順に縦積みで配置する(ComputeLayoutが全座標を一元計算)。</t>
+  </si>
+  <si>
+    <t>各スキル行に「[実キー] スキル名 Lv{n} (cd {秒}s, {mp}mp, 元素名)」をテキスト表示する。専用アイコン画像は無く、色分けと文字のみで表現する。</t>
+  </si>
+  <si>
+    <t>独自グラフィックアイコンは未実装(テキストベース)。</t>
+  </si>
+  <si>
+    <t>各スキル行の下にソケット数分の小さな矩形(DrawSocketBox)を描画し、装着中は青系の塗り+Support名、空きは暗色+「+ Empty」を表示する。ソケット拡張ボタンは上限未到達かつJeweller's Orb所持時のみ有効表示。</t>
+  </si>
+  <si>
+    <t>各Spirit行に「[Spirit N] ジェム名 Lv{x} ({コスト} spirit)」+右端にON/OFFトグルボタン(緑=ON/暗赤=OFF)を表示する。パネル上部には「Spirit: {予約}/{Max} reserved」の合計値も表示する。</t>
+  </si>
+  <si>
+    <t>ピッカー内の候補行のみ、要件未達成時に赤字着色+末尾へ理由文字列(例:Requires 32 Int)を付記する。すでに装着済みのスロット自体のグレーアウトは行わない(選べない理由は候補一覧側でのみ表現)。</t>
+  </si>
+  <si>
+    <t>Gキーでトグル。CharacterSheet/Inventoryとは非ポーズ系同士で同時表示可(タブ切替的にCharacterSheetとは排他)、PassiveTree/Vendor/KeyBindのようなポーズ系メニューを開くと自動的に閉じる。Escapeキーでも閉じられる。</t>
+  </si>
+  <si>
+    <t>GemIdentifySystemが画面中央付近に固定パネル(kPanelX=240, kPanelY=140, kPanelW=420, kPanelH=420)を表示し、上部にヘッダ、中央に候補リスト、下部に「Cancel」ボタンを配置する。</t>
+  </si>
+  <si>
+    <t>候補名(+Skill/Spiritはアップグレード時のLv表記)のみをテキストで表示する。</t>
+  </si>
+  <si>
+    <t>仕様書が求めるアイコン/カテゴリ/タグ/要求武器/要求Lv/Tier/Mana Cost/説明は未実装。</t>
+  </si>
+  <si>
+    <t>候補行を左クリックすると即座に確定(Identify)される。確認ダイアログ等の中間ステップは無い。</t>
+  </si>
+  <si>
+    <t>「Cancel」ボタンでパネルを閉じる。未確定のUncut Gemはキューに残ったままになる。</t>
+  </si>
+  <si>
+    <t>パネル内にEscapeキーのバインドは無く、ボタンクリックのみでキャンセルする。</t>
+  </si>
+  <si>
+    <t>Uncut Gemは通常のInventoryComponentグリッドには表示されない。SkillGemSystemのパネル上部に「Uncut Gems」行として、種別略称+Lv(例: Sk3/Su5/Sp1)のチップで一覧表示される。</t>
+  </si>
+  <si>
+    <t>独立したInventory画面という形ではなく、Skills Panelの一部として表示する設計。</t>
+  </si>
+  <si>
+    <t>右クリックではなく、上記チップを左クリックすることでGemIdentifySystem::Openが呼ばれる。</t>
+  </si>
+  <si>
+    <t>仕様書が求める「Inventory内でHover→Right Click」ではなく、専用チップのLeft Clickという別UIになっている。</t>
+  </si>
+  <si>
+    <t>pendingUncutGemsが上限8件に達した状態で新たなUncut Gemを拾おうとすると、ItemPickupSystemが「Uncut gem storage full」という一時メッセージ(画面下部、2.5秒間)を表示し拾得を拒否する。</t>
+  </si>
+  <si>
+    <t>専用のGemツールチップは無く、SkillGemSystemの行テキスト自体が名前/Lv/Cooldown/Mana/元素を常時表示する形になっている(ホバー時だけ出る別ウィンドウではない)。</t>
+  </si>
+  <si>
+    <t>同様にツールチップではなく、Supportピッカー/ソケット表示のテキストとして名前+要件属性値を常時表示する。</t>
+  </si>
+  <si>
+    <t>Spirit行のテキストとして名前/Lv/コストを常時表示する(Persistent Effectの詳細説明文などは表示していない)。</t>
+  </si>
+  <si>
+    <t>「暗くするだけ」ではなく、ピッカー内で赤字+理由文字列を必ず併記する方針を全ジェム種別(Skill/Support/Spirit)で統一している。ただし理由は都度その場でハードコードされた文字列であり、共通のReasonCode enumを介してはいない。</t>
+  </si>
+  <si>
+    <t>GameAction::ToggleSkillGems(既定G)。KeyBindSystemでリバインド可能。</t>
+  </si>
+  <si>
+    <t>GameAction::ToggleInventory(既定I)。Uncut Gem専用の別インベントリ画面キーは無く、Uncut GemはSkills Panel側に表示される。</t>
+  </si>
+  <si>
+    <t>Escapeキーで6つの全メニュー(CharacterSheet/Inventory/SkillGem/PassiveTree/Vendor/KeyBind)を一括で閉じる(GameScene::Update)。KeyBindSystemがリバインド待ち中はEscapeをキャンセル用に使うため、その間はメニュー閉じ処理を発動させない(awaitingRebindガード)。</t>
+  </si>
+  <si>
+    <t>GameAction::Skill1〜5(既定E/Q/R/V/F)。押下+SkillActivation::CanUseSkill成立で発動する。</t>
+  </si>
+  <si>
+    <t>専用キーは無く、地上アイテム(Uncut Gem含む)は近づいてクリックすることで拾得する(ItemPickupSystem::FindNearestPickup+左クリック)。</t>
+  </si>
+  <si>
+    <t>仕様書が想定する専用のInteract/Pickupキーは本実装には無い(クリック方式で統一)。</t>
+  </si>
+  <si>
+    <t>Skills Panel内の「Uncut Gems」チップを左クリックする操作がこれに相当する。専用のUseItem/ContextActionキーやマウス右クリックへのハードコードは無い。</t>
+  </si>
+  <si>
+    <t>GameAction::Roll(既定Space)。ジェムシステムとは直接関係しないが、Weapon要件同様スキルのDash系挙動と隣接する操作として記載。</t>
+  </si>
+  <si>
+    <t>専用の確定キーは無く、全てのジェム系UI(Skills Panel/Gem Cutting)は左クリックで確定する。キーボードでの確定操作は実装していない。</t>
+  </si>
+  <si>
+    <t>Gem Cuttingは「Cancel」ボタンのクリックのみ(キーボードのBack操作無し)。他のパネル全体はEscapeで閉じられる。</t>
+  </si>
+  <si>
+    <t>ジェム系UIには右クリック操作は存在しない(全て左クリックで統一)。装備アイテムのInventorySystemでは右クリック装備等が別途あるが、ジェム関連UIとは独立した実装。</t>
+  </si>
+  <si>
+    <t>ジェム関連ではSkill1〜5とToggleSkillGems(Gキー)がリバインド対象(GameAction列挙体、KeyBindSystemでUI操作可能)。</t>
+  </si>
+  <si>
+    <t>Skills Panel/Gem CuttingのUI内クリック操作(スロット選択/ソケット選択/候補選択/ON-OFFトグル/Cancel)は全て固定の左クリックであり、リバインド対象に含まれない(GameActionに存在しない)。</t>
+  </si>
+  <si>
+    <t>KeyBindings::Instance().Get(...)から取得した実キー文字列をSkillGemSystemが動的に埋め込んで表示する(例:Skill Gems (G to close)、各スロット行の[E]等)。文字列をハードコードせず、リバインド後は自動的に表示が追従する。</t>
+  </si>
+  <si>
+    <t>WaystoneInventoryComponent(Waystone.h)がkMaxTier=15の配列counts[15]でティア1〜15の所持数を保持する。本家Atlasの多様なMap Tier概念を単純な整数ティアのみに簡略化しており、Map固有のModifier/Layoutバリエーションは実装していない。</t>
+  </si>
+  <si>
+    <t>CollisionSystem::TrySpawnWaystoneDropが敵撃破時に判定し、BossTag持ちなら現在ティア(CampaignManager::GetEndgameMapTier)+1を確定ドロップ、MonsterRarity::Rareなら35%の確率で同ティアをドロップする(通常モンスターはドロップしない)。エンドゲームAct(CurrentAct().isEndgame)でのみ呼び出される。</t>
+  </si>
+  <si>
+    <t>タウンの拠点でポータルにEnterキーを押すとGameScene::TryOpenEndgameMapFromHubが実行され、所持中の最高ティアWaystoneを1個消費してCampaignManager::OpenEndgameMap(tier)を呼ぶ。所持が無い場合は「Need a Waystone to open a map」と表示し何も起きない。</t>
+  </si>
+  <si>
+    <t>TryOpenEndgameMapFromHubはティア15から1へ降順に走査し、counts[t-1]&gt;0の最初のティアを自動選択・消費する(個別選択UIは無い)。本家のように任意のティアを選んで出撃する自由度は無く、常に最高ティア優先の単純ロジックになっている。</t>
+  </si>
+  <si>
+    <t>マップ生成自体は通常戦闘ゾーンと同じZoneBuilder::Build/MapGeneratorを使い、Tierによる差分はtierScale=1.0+0.15*(endgameMapTier-1)という敵のHP/ATK倍率と、isEndgame時に雑魚のうち最大3体を確定Rare化する(guaranteedRares)処理のみで表現している。</t>
+  </si>
+  <si>
+    <t>ZoneBuilder::ApplyTierResistanceがbonus=min(0.75, 0.03*(endgameMapTier-1))を計算し、敵の火/冷気/電気/カオス耐性に加算する(上限90%)。エンドゲーム以外はendgameMapTierが常に1に固定されているため実質no-opになる。</t>
+  </si>
+  <si>
+    <t>マップクリア条件は通常戦闘ゾーンと同一で、GameScene::UpdateがPlayerTagを持たない生存エンティティが0になった時点でAdvanceToNextZoneを呼ぶ。ボス/Rare個別の討伐チェックはなく「場に敵がいなくなったら終了」という単純な全滅判定のみ。</t>
+  </si>
+  <si>
+    <t>このチェックはAllyTagComponent(Permanent Minion)を除外していないため、自分の召喚ミニオンが生存している間はクリア判定が成立しない副作用がある(実プレイでは要検証)。</t>
+  </si>
+  <si>
+    <t>ZoneBuilder::Buildがゾーン定義のenemyCount体をSpawnTrashで配置し、zone.isBossZoneならSpawnBossで専用ボスを1体追加する。エンドゲームでは前述のguaranteedRares(最大3体)により雑魚の一部が強制的にRare化される。</t>
+  </si>
+  <si>
+    <t>CampaignManager::BuildActsがAct1(海岸)→Act2(砂漠)→幕間I(静寂)→Act3(王都)→Act4(山嶺)→幕間II(終端)→Endgame(地図の狭間)の7つのActDefinitionを固定順で構築する。各非エンドゲームActはTown+Combat2〜3体+Boss1体のゾーン列を持つ一本道構成。</t>
+  </si>
+  <si>
+    <t>本家の「Act1〜3をNormal→Cruelで2周」という構成ではなく、6つの異なるエリアを1本道で進む独自構成(AI/DECISIONS.mdに既記載)。</t>
+  </si>
+  <si>
+    <t>タウンではm_hasPortalのポータルにEnterキーで近接すると次ゾーンへ、戦闘ゾーンでは敵全滅で自動的にAdvanceToNextZoneが呼ばれ次のゾーンへ遷移する。CampaignManager::CompleteCurrentZoneAndAdvanceがm_zoneIndexをインクリメントし、Act内の最後のゾーンならm_actIndexを進めてタウンへ戻す。</t>
+  </si>
+  <si>
+    <t>CompleteCurrentZoneAndAdvanceは非エンドゲームAct(全6つ)をクリアするたびにm_savedEquipment.baseStatsの火/冷気/電気耐性へ-10%を直接加算する(カオス耐性は対象外)。全6幕クリアで最大-60%になり、ConsumePendingResPenaltyNotice経由で1回だけHUDトースト通知される。</t>
+  </si>
+  <si>
+    <t>本家の「Cruel再攻略時の耐性ペナルティ」に相当する仕様として、幕クリア数で代替実装している(AI/DECISIONS.mdに既記載)。</t>
+  </si>
+  <si>
+    <t>CombatMath::CalcHitChance(accuracy, evasion)がchance = accuracy/(accuracy+evasion*0.5)を計算し、5%〜100%にクランプする(accuracy&lt;=0なら常に5%)。RollHitはこの確率で乱数比較するのみのシンプルな実装。</t>
+  </si>
+  <si>
+    <t>CombatMath::CalcArmourMitigation(armour, incomingPhysicalDamage)がmitigation = armour/(armour+10*incomingDamage)を計算し、0〜90%にクランプする。物理ダメージにのみ適用され、ApplyDamage内で他の軽減より先に処理される。</t>
+  </si>
+  <si>
+    <t>CombatMath::GetResistanceが対象の火/冷気/電気/カオス耐性値を-100%〜75%にクランプして返し、ApplyDamageでdmg *= (1-resistance)として乗算適用する。耐性はマイナス値も許容しており、Act耐性ペナルティ(-60%まで)の累積がそのまま反映される設計。</t>
+  </si>
+  <si>
+    <t>ApplyDamageはカオス以外の属性ダメージのみエナジーシールドで吸収可能で、Armour軽減→耐性軽減の後にcurrentESから先に減算し(absorbed = min(ES, dmg))、超過分のみHPへ通す。吸収が発生するとesRegenDelayを3秒にリセットする。</t>
+  </si>
+  <si>
+    <t>カオスダメージはES無視でHPへ直接通る(本家のChaos Damage bypasses ESに準拠)。</t>
+  </si>
+  <si>
+    <t>CombatMath::RollBlock(blockChance)が0〜75%にクランプした確率でロールし、成功すればそのヒットのダメージを丸ごと0にする(ApplyDamageの最初のガード条件)。blockChanceは盾専用ではなくAffixStat::BlockChanceという汎用サフィックスとしてどの装備にも付与されうる。</t>
+  </si>
+  <si>
+    <t>本家は盾/杖等の特定装備専用だが、本実装は盾スロット自体が無いため汎用サフィックス化している(AI/DECISIONS.mdに既記載)。</t>
+  </si>
+  <si>
+    <t>CombatMath::RollCrit(critChance)が単純な確率ロールを行い、成功時はApplyDamage呼び出し側(CollisionSystem)でrawDamage *= critDamageとして攻撃側のcritDamage値を乗算する。クリティカルダメージ自体の耐性・軽減判定への影響はない。</t>
+  </si>
+  <si>
+    <t>CharacterStatsComponent::leechPercent(命中ダメージの一部をpendingLeechへ積算)とleechRateCap(既定0.20、maxHPに対する秒間回復上限の割合)を持ち、StatusEffectSystem::Updateがmax Drain = maxHP*leechRateCap*dtを上限にpendingLeechから回復を消化する。</t>
+  </si>
+  <si>
+    <t>CombatMath::ApplyAilmentOnHitはFire属性ヒット時にRollAilmentChance(クリティカルなら確定、それ以外はダメージ量/maxHPの25%に比例)で発生判定し、成功するとigniteDps=hitDamage*0.5・igniteRemaining=4.0秒を設定する(StatusEffectSystemが毎フレームcurrentHP -= igniteDps*dtで処理)。</t>
+  </si>
+  <si>
+    <t>Cold属性ヒットはRollAilmentChance判定に関わらず必ずchillRemaining=2.0秒・chillSlowPercent=0.3(30%減速)を付与し、さらにRollAilmentChance成功時のみfreezeRemaining=1.0秒(StatusEffectsComponent::IsHardLocked()により移動完全ロック)を追加付与する。</t>
+  </si>
+  <si>
+    <t>Freezeはfreeze Remaining単独ではなくStun同様IsHardLocked()経由で速度をゼロにする実装。</t>
+  </si>
+  <si>
+    <t>Lightning属性ヒットはRollAilmentChance成功時のみshockRemaining=3.0秒・shockIncreasedDamageTaken=0.2を付与し、その間は対象が受ける全ダメージにrawDamage *= (1+0.2)が乗算される(CollisionSystem側で参照)。</t>
+  </si>
+  <si>
+    <t>Chaos属性ヒットは確率判定なしで必ずpoisonStacksに{damagePerSecond: hitDamage*0.3, remaining: 2.0秒}を1スタック追加する(std::vector&lt;PoisonStack&gt;で多重スタック可能、StatusEffectSystemが各スタックを個別に減算・期限切れで除去)。</t>
+  </si>
+  <si>
+    <t>Ignite/Bleedと異なり単一値の上書きではなく独立スタックとして累積する点が特徴。</t>
+  </si>
+  <si>
+    <t>Physical属性ヒットはRollAilmentChance成功時のみbleedDps=hitDamage*0.3・bleedRemaining=5.0秒を設定する(既存のBleedを上書き、Igniteと同じ単一値方式)。</t>
+  </si>
+  <si>
+    <t>ApplyAilmentOnHitの末尾で属性を問わずhitDamage &gt;= targetMaxHP*0.15ならstunRemaining=0.3秒を付与し、その間IsHardLocked()により対象の速度を強制的にゼロにする(移動完全ロック、Freezeと同じ扱い)。</t>
+  </si>
+  <si>
+    <t>EquipSlot列挙(Item.h)がWeapon/BodyArmour/Helmet/Gloves/Boots/Ring1/Ring2/Amulet/Beltの9スロット+Countを定義し、EquipmentComponent::slotsはstd::array&lt;std::optional&lt;ItemComponent&gt;,9&gt;で保持する。</t>
+  </si>
+  <si>
+    <t>ItemComponent::PowerScore()はbaseValue + Σaffix.valueという単純な合計値を返し、EquipmentSystem::TryEquipが装備中アイテムのPowerScore()と新規アイテムのそれを比較して「上回った場合のみ装備」する自動判定に使う。</t>
+  </si>
+  <si>
+    <t>本家のような複雑なDPS/防御力の重み付け計算ではなく、素の数値合計のみの簡易比較。</t>
+  </si>
+  <si>
+    <t>ItemFactory::PrefixPool()はIncreasedAttackDamage/FlatArmour/FlatEvasion/FlatESの4種、SuffixPool()はFireRes/ColdRes/LightningRes/ChaosRes/FlatLife/FlatMana/CritChance/MoveSpeed/FlatAccuracy/BlockChance/FlatSpirit(計11種)を持つ固定プールで、レアリティごとにこのプールからシャッフル抽選する。</t>
+  </si>
+  <si>
+    <t>FlatSpiritはジェムシステム(Permanent Minion)実装に伴い追加されたサフィックス。</t>
+  </si>
+  <si>
+    <t>GenerateItemは選ばれたAffixのvalueに対し(1.0+itemLevel*0.03)*variance(0.85〜1.15の一様乱数)を掛けてロールする。Tierという明示的な段階は無く、Item Levelと乱数幅による連続的なスケーリングのみで表現している。</t>
+  </si>
+  <si>
+    <t>ItemAffix::tierフィールド自体は存在するが常に1固定で、Tier別の異なる基礎値テーブルは未実装。</t>
+  </si>
+  <si>
+    <t>ItemFactory::RollRarityは0〜1の乱数で8%未満をRare、30%未満(8%以上)をMagic、それ以外をNormalとする単純な閾値抽選。GenerateItemはレアリティに応じてMagicなら1つ、Rareなら1〜3個ずつのPrefix/Suffixを付与する。</t>
+  </si>
+  <si>
+    <t>Item Level(itemLevel)はBaseValueForで武器/防具の基礎値に線形加算され(例: 武器は5.0+itemLevel*1.5)、Affix値にも1.0+itemLevel*0.03の乗数として効く。ドロップ元のitemLevelはCollisionSystem側でモンスターのmaxHPからclamp(maxHP/15,1,100)として算出される。</t>
+  </si>
+  <si>
+    <t>ItemFactory::SellValueは(itemLevel*2.0+affixes.size()*3.0)*rarityMultiplier+1で算出し、rarityMultiplierはMagic=2.0/Rare=4.0/Unique=8.0(Normalは1.0)。Vendorへの売却・インベントリ満杯時の自動売却の両方でこの関数を共有する。</t>
+  </si>
+  <si>
+    <t>バッグはItemUIHelpers::kBagGridCols=6×kBagGridRows=4の24マスグリッドで、ItemGridSize(slot)がスロット種別ごとの専有サイズ(武器1x3、胴防具2x3、兜/手袋/靴2x2、ベルト2x1、指輪/首飾り1x1)を返す。空き判定はマス数ではなくBagRegionFreeによるWxH形状の実際の収まりで行う。</t>
+  </si>
+  <si>
+    <t>ItemPickupSystem::UpdateはクリックしたアイテムをFindBagFreeSpaceで配置先を探し、見つかれば InventoryComponent::items へ追加、見つからなければItemFactory::SellValue分のゴールドを即座に付与して「Inventory full - sold ...」と表示する自動売却フォールバックになっている。</t>
+  </si>
+  <si>
+    <t>InventorySystemは左クリックのドラッグでバッグ内移動・装備⇔バッグの入れ替えを行い(HandleDrop)、右クリックはQuickEquip/QuickUnequipで即時装備/解除する。パネル外へドロップするとDropDraggedItemOnGroundでアイテムを足元に投棄する(破棄)。</t>
+  </si>
+  <si>
+    <t>売却操作はこの画面には無く、商人NPCへ話しかける必要がある(AI/DECISIONS.mdに既記載)。</t>
+  </si>
+  <si>
+    <t>CurrencySystem::ApplyCurrencyが拾得と同時に対象アイテムへ即時適用する方式で、Transmutation(Normal→Magic+Affix1個)/Alchemy・Chance(→Rareへ再生成)/Regal(Magic→Rare+Affix追加)/Chaos(Rareを再生成)/Augmentation(Magicの不足側Affixを追加)/Annulment(Affixを1つランダム除去)/Scouring(Normalへ初期化)を実装する。Regret Orbはパッシブ解放用、Jeweller's Orbはスキルジェムのソケット拡張用として即時適用せず所持数へ蓄積する。</t>
+  </si>
+  <si>
+    <t>各Currencyは FindEligibleSlot で条件を満たす装備中アイテムを自動選択して適用するため、本家のように「対象アイテムへドラッグして使う」操作は無い。</t>
+  </si>
+  <si>
+    <t>VendorSystemはBuy(在庫購入)/Buyback(売却したアイテムの買い戻し)の2タブ構成で、購入価格はBuyPrice = SellValue*3、売却はバッグアイテムをCtrl+左クリックまたは左パネルへドラッグで行い、売った額そのままでBuybackタブ(最大kMaxBuyback=12件、超過で最古を破棄)から買い戻せる。</t>
+  </si>
+  <si>
+    <t>VendorSystem::RerollPrice(level) = 20+level*4ゴールドを消費してGameAction::VendorReroll(既定Tキー)で在庫6点を再生成する(TryReroll)。また話しかけ時にプレイヤーレベルが前回と異なれば無料で自動再生成される(Open内のplayerLevel != m_stockLevel判定)。</t>
+  </si>
+  <si>
+    <t>LevelSystem::CalcXPToNextLevel(level) = 100*level^1.5という指数的な必要経験値カーブを使用し、GrantXPがwhileループで複数レベル一気に上がる場合にも対応する。</t>
+  </si>
+  <si>
+    <t>レベルアップ毎にpassivePointsを1増やし、equipment.baseStatsへmaxHP+8・maxMP+6・atk+1.5を恒久加算する(装備変更で消えないようbaseStats側に加算)。明示的なレベル上限は実装されておらず無制限に上昇し続ける。</t>
+  </si>
+  <si>
+    <t>PassiveTreeDataが中心のスタートノード(id0)からoffense/defense/mobility/resistの4方向へAddChainで再帰的に分岐するツリーを構築し、計53ノードで構成される(ROADMAPに既記載)。</t>
+  </si>
+  <si>
+    <t>PassiveTreeSystem::TryAllocateは対象ノードのneighborsのいずれかが既に割り振り済みでない限り割り振りを拒否する(スタートノード含め隣接必須)。所持passivePointsが0の場合も拒否される。</t>
+  </si>
+  <si>
+    <t>TryDeallocateはCharacterStatsComponent::regretOrbsを1個消費して対象ノードを解放し、passivePointsを1返却する。CanRemoveWithoutDisconnectingがBFSで「他の割り振り済みノードがスタートから到達不能にならないか」を検証し、孤立させる解放は拒否する。</t>
+  </si>
+  <si>
+    <t>本家のようなキー操作(Backspaceキー)を割り当てて解放する実装だが詳細はPassiveTreeSystem.hの入力処理側で行われる。</t>
+  </si>
+  <si>
+    <t>RangedAttackerComponent等の専用タグを持たない通常モンスターはEnemyAISystemが単純にプレイヤー方向へmoveSpeedで直進し、距離10px未満で停止する。ダメージは専用の攻撃処理を持たず、CollisionSystemの接触ダメージ判定(命中率/物理軽減/属性耐性込み)にそのまま乗る。</t>
+  </si>
+  <si>
+    <t>RangedAttackerComponentはpreferredRange=220未満なら後退(kite)、attackRange=320超過なら接近、その間は静止してEnemyRangedAttackSystemがcooldownTime=2.2秒毎にdamagePercent=60%(atk比)・projectileSpeed=260の弾を発射する。</t>
+  </si>
+  <si>
+    <t>AreaAttackerComponentはtriggerRange=90まで接近後に根停まりし、telegraphTime=0.8秒の予兆後に半径radius=100・damagePercent=90%の範囲攻撃をEnemyAreaAttackSystemが発生させ、cooldownTime=3.2秒のクールダウンに入る。</t>
+  </si>
+  <si>
+    <t>SummonerComponentはプレイヤーがtriggerRange=260以内にいる間、summonInterval=5.0秒毎に自身のHP/ATKのstatScale=0.5倍の雑魚をEntitySpawner::CreateEnemy経由で周囲に召喚し、maxActiveSummons=2体まで同時生存を許容する(EnemySummonSystemが死亡した召喚体をactiveSummonIdsから都度除去)。</t>
+  </si>
+  <si>
+    <t>ChargerComponentはtriggerRange=200まで通常追跡した後telegraphTime=0.5秒根停まりで予兆し、その後chargeDuration=0.4秒の間chargeSpeedMultiplier=3.5倍速度で直線突進する(chargeDirectionは予兆終了時点で固定)。突進中のダメージは専用処理を持たず通常の接触ダメージ判定に乗る。</t>
+  </si>
+  <si>
+    <t>BossPhaseComponent::enrageThreshold=0.5(HP50%)を下回った時点でBossPhaseSystemが一度だけatk*=1.6・moveSpeed*=1.35を適用し、CircleComponentの色を赤へ変更、カメラシェイクとHUDメッセージ(3秒間)を発生させる(hasEnragedフラグで再発動を防止)。</t>
+  </si>
+  <si>
+    <t>CharacterSheetSystemはPoE2本家準拠の並びで「概要(Lv/XP/パッシブポイント)→属性(STR/DEX/INT、色分け)→主要ステータス(Life/Mana/ES/Spiritの現在値/最大値+秒間回復量)→耐性4種(数値+上限75%表示)→詳細な防御(Armour/Evasion/Block率)→その他(移動速度/命中率/リーチ%)」の順に区分見出し付きで表示する。</t>
+  </si>
+  <si>
+    <t>装備欄・攻撃力等のスキル依存ステータスは意図的に含まない(Iキーのインベントリ/スキルジェムパネル側の責務、AI/DECISIONS.mdに既記載)。</t>
+  </si>
+  <si>
+    <t>InventorySystemのパネルは760x400pxで、左にペーパードール(9装備スロット)・右に6x4グリッドのバッグを表示する。ドラッグ&amp;ドロップで移動/装備入替、右クリックで即時装備/解除、パネル外ドロップで破棄という操作体系(項目34と同一)。</t>
+  </si>
+  <si>
+    <t>KeyBindings::GameActionはMoveUp/Down/Left/Right、Roll、Skill1〜5、ToggleCharacterSheet/Inventory/PassiveTree/SkillGems、VendorRerollの計14項目のみがリバインド対象で、既定値はW/A/S/D、Space、E/Q/R/V/F、C/I/P/G、Tとなっている(KeyBindings::ResetToDefaults)。</t>
+  </si>
+  <si>
+    <t>各UIパネル共通の固定操作として、カーソル移動(Up/Down/Left/Right)・確定(Enter)・戻る系(Backspace/Delete)・売却(X、Vendor文脈)がハードコードされており、GameActionには含まれずリバインド対象外となっている(UIナビゲーションとゲームプレイ操作を区別する方針)。</t>
+  </si>
+  <si>
+    <t>マウスの左クリック(選択/ドラッグ開始)・右クリック(装備/解除)・Ctrl+左クリック(Vendorでの即売却)も同様に固定。</t>
+  </si>
+  <si>
+    <t>CampaignManager::SaveToDiskはactIndex/zoneIndex/endgameMapTier/hasSavedPlayer/isHardcoreのフラグに加え、stats./base.(CharacterStatsComponent一式)、装備9スロット、インベントリ全アイテム、パッシブツリー割り振り済みノード、所持ジェム(ownedGems、レベル/ソケット/装着サポート込み)、未鑑定Uncut Gemキュー(pendingUncutGems)、スキル/スピリットのロードアウトとON/OFF状態、Waystone所持数(15ティア分)をフラットなkey=value形式で保存する。</t>
+  </si>
+  <si>
+    <t>LoadFromDiskはまずファイル全体をkey=valueの連想配列へ読み込んだ上で、actIndex/zoneIndex等のカウンタ→統計値→装備→インベントリ→パッシブツリー→所持ジェム→未鑑定ジェムキュー→スキル/スピリットロードアウト→Waystoneの順にメンバ変数へ復元する。実際のECSコンポーネントへの反映(GameSceneコンストラクタ)はさらにその後、装備のRecalculateStats実行→スキルのBuildEquippedSkillData再構築という順で行われる。</t>
+  </si>
+  <si>
+    <t>新フィールドが存在しない旧セーブはGetI等のデフォルト値で自然に空/初期値へフォールバックする設計(既存の!GetSavedX().empty()ガードパターン)。</t>
+  </si>
+  <si>
+    <t>DebugManager(F1トグル)はGame Screen表示・Scene Management(シーン切替コンボ)・Log Window(未実装プレースホルダ)・Camera Control(ズームスライダー)・Performance(FPS/CPU/メモリ)・Language設定の6パネルを提供する。加えてGameScene::RenderImGui側に「Game Tools」(Spawn Enemyボタン)と「Gem Debug」(Uncut Gemスポーン/STR・DEX・INT編集/Max Spirit・現在マナ編集/Jeweller's Orb付与/Spirit予約内訳・最終スキル計算値・サポート適合判定の表示)が実装されている。</t>
+  </si>
+  <si>
+    <t>RenderOtherDebugInfoという未使用の空メソッドがDebugManagerに残っている(将来用の未使用プレースホルダ)。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3346,6 +4332,24 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -3390,12 +4394,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3408,8 +4415,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -11625,6 +12642,1831 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7746AA20-CD5B-4A4B-9054-A829ED792FBF}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4305146D-4410-469F-96CE-560F74C0210F}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F172ED88-FC6D-4DDE-9A60-D88BE4CC24B8}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF1BA22-0B78-4E8C-8347-F719C9AB71B1}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="187.5" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B2E000-ACCD-44A6-B680-A4CF18A9AF1C}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="46.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A17" s="3">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A18" s="3">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A20" s="3">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A21" s="3">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{443482F7-7701-49A9-AEDB-D400D1CE882D}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="46.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A17" s="3">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47FF9922-D181-4014-9303-81E7C5755F06}">
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="18.625" customWidth="1"/>
+    <col min="3" max="3" width="22.625" customWidth="1"/>
+    <col min="4" max="4" width="45.625" customWidth="1"/>
+    <col min="5" max="5" width="50.625" customWidth="1"/>
+    <col min="6" max="6" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="75" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:6" ht="75" x14ac:dyDescent="0.4">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:6" ht="75" x14ac:dyDescent="0.4">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="75" x14ac:dyDescent="0.4">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="168.75" x14ac:dyDescent="0.4">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" spans="1:6" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="1:6" ht="75" x14ac:dyDescent="0.4">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F41" s="3"/>
+    </row>
+    <row r="42" spans="1:6" ht="75" x14ac:dyDescent="0.4">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="F42" s="3"/>
+    </row>
+    <row r="43" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F45" s="3"/>
+    </row>
+    <row r="46" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F46" s="3"/>
+    </row>
+    <row r="47" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F47" s="3"/>
+    </row>
+    <row r="48" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F48" s="3"/>
+    </row>
+    <row r="49" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F49" s="3"/>
+    </row>
+    <row r="50" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F51" s="3"/>
+    </row>
+    <row r="52" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F52" s="3"/>
+    </row>
+    <row r="53" spans="1:6" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="187.5" x14ac:dyDescent="0.4">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F54" s="3"/>
+    </row>
+    <row r="55" spans="1:6" ht="150" x14ac:dyDescent="0.4">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="168.75" x14ac:dyDescent="0.4">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75622AD1-D3B8-4FA3-B036-78041C75B546}">
   <dimension ref="A1:E28"/>
@@ -12090,4 +14932,1731 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{286BBEDE-D1E8-40E1-8CE6-B1FA902DE810}">
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="26.625" customWidth="1"/>
+    <col min="4" max="4" width="40.625" customWidth="1"/>
+    <col min="5" max="5" width="50.625" customWidth="1"/>
+    <col min="6" max="6" width="30.625" customWidth="1"/>
+    <col min="7" max="7" width="24.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="6" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="6" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="6" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="6" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="6" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="6" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="6" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="6" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="6" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="6" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="6" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="6" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="6" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="6" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="6" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="6" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="6" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="6" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="6" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="6" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="6" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="6" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="6" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="6" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="6" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="6" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="6" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="6" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="6" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="G2" location="'SkillGem仕様'!A1" display="SkillGem仕様" xr:uid="{551DEA15-B46F-43CA-8912-1283CEE4EACB}"/>
+    <hyperlink ref="G3" location="'SkillGem仕様'!A1" display="SkillGem仕様" xr:uid="{8ACDB130-7F87-4E9B-84C9-5B3D15C323DE}"/>
+    <hyperlink ref="G4" location="'SkillGem仕様'!A1" display="SkillGem仕様" xr:uid="{748E3B56-BBC3-4A65-ABB2-38A428011B5E}"/>
+    <hyperlink ref="G5" location="'SupportGem仕様'!A1" display="SupportGem仕様" xr:uid="{A6E468A7-F788-4834-80D7-669C813A97E0}"/>
+    <hyperlink ref="G6" location="'SupportGem仕様'!A1" display="SupportGem仕様" xr:uid="{71FDEBB0-168B-4307-A072-F6A1913BA46E}"/>
+    <hyperlink ref="G7" location="'SupportGem仕様'!A1" display="SupportGem仕様" xr:uid="{5B2C72BE-9AD3-4690-A74D-A10A9F8A8136}"/>
+    <hyperlink ref="G8" location="'SupportGem仕様'!A1" display="SupportGem仕様" xr:uid="{EE140369-69FC-406C-9A76-198E2DC19B1B}"/>
+    <hyperlink ref="G9" location="'SpiritGem_Persistent仕様'!A1" display="SpiritGem_Persistent仕様" xr:uid="{0C0E9C43-C289-44BC-B482-0D454EF86956}"/>
+    <hyperlink ref="G10" location="'SpiritGem_Persistent仕様'!A1" display="SpiritGem_Persistent仕様" xr:uid="{5AA36A7A-F324-425E-A7C9-5F5C417B91A7}"/>
+    <hyperlink ref="G11" location="'SpiritGem_Persistent仕様'!A1" display="SpiritGem_Persistent仕様" xr:uid="{2854F186-F13D-4073-A2AA-5E53908FEE1E}"/>
+    <hyperlink ref="G12" location="'SpiritGem_Persistent仕様'!A1" display="SpiritGem_Persistent仕様" xr:uid="{6624C5E0-506B-4AAB-964E-769A4C0BFCF4}"/>
+    <hyperlink ref="G13" location="'Spiritリソース仕様'!A1" display="Spiritリソース仕様" xr:uid="{864CCF0D-9597-4941-9417-F9DED8F09C71}"/>
+    <hyperlink ref="G14" location="'Spiritリソース仕様'!A1" display="Spiritリソース仕様" xr:uid="{C1AC78BE-B47A-4A7A-946C-8F538678B9B7}"/>
+    <hyperlink ref="G15" location="'Spiritリソース仕様'!A1" display="Spiritリソース仕様" xr:uid="{2359633A-1F54-433C-A33B-CA67F5033987}"/>
+    <hyperlink ref="G16" location="'UncutGem仕様'!A1" display="UncutGem仕様" xr:uid="{4292FE5A-0CDD-4148-A35C-0E022546C044}"/>
+    <hyperlink ref="G17" location="'UncutGem仕様'!A1" display="UncutGem仕様" xr:uid="{CC584C5F-867F-4714-BE6E-5609A362A4D2}"/>
+    <hyperlink ref="G18" location="'UncutGem仕様'!A1" display="UncutGem仕様" xr:uid="{F9260C54-AC0B-4871-8EF8-0F3112E29DCD}"/>
+    <hyperlink ref="G19" location="'UncutGem仕様'!A1" display="UncutGem仕様" xr:uid="{F02E03E7-64C4-4D22-BBED-62278677DE38}"/>
+    <hyperlink ref="G20" location="'Gemcutting仕様'!A1" display="Gemcutting仕様" xr:uid="{A0042CD9-755F-4BE4-8DA0-FEF5B3DED59D}"/>
+    <hyperlink ref="G21" location="'Gemcutting仕様'!A1" display="Gemcutting仕様" xr:uid="{D3AEF7F2-52CC-4D9D-AFA6-490B860D8797}"/>
+    <hyperlink ref="G22" location="'Gemcutting仕様'!A1" display="Gemcutting仕様" xr:uid="{1AD466F5-E172-4875-AC88-464E40DA5D99}"/>
+    <hyperlink ref="G23" location="'SkillsPanel仕様'!A1" display="SkillsPanel仕様" xr:uid="{AC6CC865-7CDC-44F2-A42C-25CB21CA6966}"/>
+    <hyperlink ref="G24" location="'SkillsPanel仕様'!A1" display="SkillsPanel仕様" xr:uid="{62359AE5-37C8-479D-B241-5A0864235C94}"/>
+    <hyperlink ref="G25" location="'SkillBar_KeyBind仕様'!A1" display="SkillBar_KeyBind仕様" xr:uid="{478B0D1B-F5D1-4D7C-AFFD-15FD5B720470}"/>
+    <hyperlink ref="G26" location="'SkillBar_KeyBind仕様'!A1" display="SkillBar_KeyBind仕様" xr:uid="{805AF52F-AC43-434F-9512-F165AA722C30}"/>
+    <hyperlink ref="G27" location="'SkillActivation仕様'!A1" display="SkillActivation仕様" xr:uid="{F5179A0B-C9F7-4366-942C-9EED0F148B17}"/>
+    <hyperlink ref="G28" location="'SkillActivation仕様'!A1" display="SkillActivation仕様" xr:uid="{982B104E-F48D-4AAC-A907-D5A7E838EE12}"/>
+    <hyperlink ref="G29" location="'SaveLoad仕様'!A1" display="SaveLoad仕様" xr:uid="{965F7107-53AB-4A4F-AA2B-F8223C7B0F0B}"/>
+    <hyperlink ref="G30" location="'SaveLoad仕様'!A1" display="SaveLoad仕様" xr:uid="{A303BEBA-9963-4D4A-BC59-99CEBA5EE332}"/>
+    <hyperlink ref="G31" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{12CFD601-8F2C-4AA8-9093-64FDD4FDB018}"/>
+    <hyperlink ref="G32" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{449D8D4B-98D3-48AE-9D4C-ACED5BB9F109}"/>
+    <hyperlink ref="G33" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{C7F41FD6-13B5-426B-AD7D-FB133CEDBDB7}"/>
+    <hyperlink ref="G34" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{C8F46852-7BB3-4EAC-AEC0-40180C0989BA}"/>
+    <hyperlink ref="G35" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{4F72B77E-AFFF-4C8C-B03F-461CEBF48158}"/>
+    <hyperlink ref="G36" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{FEB18EDE-043A-4545-A695-C9F1EC2A5123}"/>
+    <hyperlink ref="G37" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{8034814F-1666-4851-B937-D807D64CD7AB}"/>
+    <hyperlink ref="G38" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{97FDFDA7-935A-406D-82FD-04473DB904B2}"/>
+    <hyperlink ref="G39" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{1787B404-7BAB-44F1-99AE-AD047F0A6D7B}"/>
+    <hyperlink ref="G40" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{5415FD57-EBEC-4638-88DE-163B488C1378}"/>
+    <hyperlink ref="G41" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{D64C28DE-6934-4477-851B-8F43C9504D42}"/>
+    <hyperlink ref="G42" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{8EFA8ED4-CAF3-473E-819D-DEE9C325AA3F}"/>
+    <hyperlink ref="G43" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{95419683-0360-4C6C-99FF-7A5B69910888}"/>
+    <hyperlink ref="G44" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{6E3B8B63-C340-40A9-9EF1-71C835653AC5}"/>
+    <hyperlink ref="G45" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{653F8C3A-14A2-488C-9A80-2D114818129A}"/>
+    <hyperlink ref="G46" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{F8290C4C-E648-4464-AACB-654AD302E3FF}"/>
+    <hyperlink ref="G47" location="'画面仕様_ジェム関連'!A1" display="画面仕様_ジェム関連" xr:uid="{4AEE9A90-45F5-4309-B151-D898003FC92A}"/>
+    <hyperlink ref="G48" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{AAB2A39F-2AF5-4090-B2BF-8354473F7BF1}"/>
+    <hyperlink ref="G49" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{6EA92A03-622A-459D-B813-FAE5D3D02E59}"/>
+    <hyperlink ref="G50" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{BF4F4005-F9F7-444D-97F5-EB3343D9F7D5}"/>
+    <hyperlink ref="G51" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{6B06F386-7131-479A-AE51-935F9D6162DF}"/>
+    <hyperlink ref="G52" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{15B67B74-6758-4CC2-A3FC-DB25E4E5B25C}"/>
+    <hyperlink ref="G53" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{D50E1C55-32B3-4983-A060-8678283C2147}"/>
+    <hyperlink ref="G54" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{4EC0CF3B-8A78-460A-B35B-2089092AC67D}"/>
+    <hyperlink ref="G55" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{A633C828-E5F3-4819-9020-582B358BC635}"/>
+    <hyperlink ref="G56" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{66B24C02-1343-4F78-B204-4C4F01465A0D}"/>
+    <hyperlink ref="G57" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{2CC97435-D73F-4E89-89AD-D0AE843768E6}"/>
+    <hyperlink ref="G58" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{F9294D97-486A-4FBD-90B6-31999CFD6F5C}"/>
+    <hyperlink ref="G59" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{0DA8BB88-AB33-4BC2-9C0F-DD188735F2AA}"/>
+    <hyperlink ref="G60" location="'キー仕様_ジェム関連'!A1" display="キー仕様_ジェム関連" xr:uid="{46C13470-02BE-47C9-A34F-42AF2A2EF861}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{499A7F54-147D-4296-9B83-E22EF2EEC54D}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="150" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0ECCF95-41FE-46A9-961E-30B221119FF2}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733D6034-D325-4153-B5F6-0430651B697C}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D70463F-8ABD-4E5D-AEC5-5ECD927CDDD9}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="150" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4BD60CF-23CF-4A8D-BFEC-B0896D523FCA}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B851B4ED-44A0-4CB4-AC9D-30B0D63E809F}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+    <col min="4" max="4" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>